--- a/keypoint.xlsx
+++ b/keypoint.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="817">
   <si>
     <t>id</t>
   </si>
@@ -41,34 +41,2443 @@
     <t>后半段</t>
   </si>
   <si>
-    <t>分?</t>
-  </si>
-  <si>
-    <t>宅建士証の有効期間は</t>
-  </si>
-  <si>
-    <t>年。</t>
-  </si>
-  <si>
-    <t>宅建業法</t>
-  </si>
-  <si>
-    <t>宅建業免許の有効期間は</t>
-  </si>
-  <si>
-    <t>成年年齢は</t>
-  </si>
-  <si>
-    <t>歳。</t>
-  </si>
-  <si>
-    <t>民法</t>
-  </si>
-  <si>
-    <t>宅建業者は、事務所ごとに専任の宅建士を</t>
-  </si>
-  <si>
-    <t>人以上置く。</t>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>商号或者名称</t>
+  </si>
+  <si>
+    <t>免许申请书记载事项 1：</t>
+  </si>
+  <si>
+    <t>宅建业法</t>
+  </si>
+  <si>
+    <t>法人：役员（非常勤也要）、政令使用人的氏名</t>
+  </si>
+  <si>
+    <t>免许申请书记载事项 2：</t>
+  </si>
+  <si>
+    <t>个人：政令使用人的氏名</t>
+  </si>
+  <si>
+    <t>免许申请书记载事项 3：</t>
+  </si>
+  <si>
+    <t>事务所名称、所在地</t>
+  </si>
+  <si>
+    <t>免许申请书记载事项 4：</t>
+  </si>
+  <si>
+    <t>各事务所的专任宅建士的氏名</t>
+  </si>
+  <si>
+    <t>免许申请书记载事项 5：</t>
+  </si>
+  <si>
+    <t>宅建业以外的事业种类</t>
+  </si>
+  <si>
+    <t>免许申请书记载事项 6：</t>
+  </si>
+  <si>
+    <t>1~5，6宅建业以外的事业不用</t>
+  </si>
+  <si>
+    <t>申请书有更改的话需要届出的内容：</t>
+  </si>
+  <si>
+    <t>商号或名称</t>
+  </si>
+  <si>
+    <t>交付的免许证记载内容1：</t>
+  </si>
+  <si>
+    <t>代表者的氏名</t>
+  </si>
+  <si>
+    <t>交付的免许证记载内容2：</t>
+  </si>
+  <si>
+    <t>主事务所所在地</t>
+  </si>
+  <si>
+    <t>交付的免许证记载内容3：</t>
+  </si>
+  <si>
+    <t>免许证番号</t>
+  </si>
+  <si>
+    <t>交付的免许证记载内容4：</t>
+  </si>
+  <si>
+    <t>免许有效期</t>
+  </si>
+  <si>
+    <t>交付的免许证记载内容5：</t>
+  </si>
+  <si>
+    <t>更换免许</t>
+  </si>
+  <si>
+    <t>免许证需要返纳的情况1：</t>
+  </si>
+  <si>
+    <t>免许取消处分</t>
+  </si>
+  <si>
+    <t>免许证需要返纳的情况2：</t>
+  </si>
+  <si>
+    <t>找到丢失的免许证</t>
+  </si>
+  <si>
+    <t>免许证需要返纳的情况3：</t>
+  </si>
+  <si>
+    <t>废业届出</t>
+  </si>
+  <si>
+    <t>免许证需要返纳的情况4：</t>
+  </si>
+  <si>
+    <t>免许证番号和年月日</t>
+  </si>
+  <si>
+    <t>宅建业者名簿记载内容1：</t>
+  </si>
+  <si>
+    <t>宅建业者名簿记载内容2：</t>
+  </si>
+  <si>
+    <t>法人役员或政令使用人</t>
+  </si>
+  <si>
+    <t>宅建业者名簿记载内容3：</t>
+  </si>
+  <si>
+    <t>个人政令使用人</t>
+  </si>
+  <si>
+    <t>宅建业者名簿记载内容4：</t>
+  </si>
+  <si>
+    <t>事务所名称和所在地</t>
+  </si>
+  <si>
+    <t>宅建业者名簿记载内容5：</t>
+  </si>
+  <si>
+    <t>宅建业以外事业种类</t>
+  </si>
+  <si>
+    <t>宅建业者名簿记载内容6：</t>
+  </si>
+  <si>
+    <t>指示处分或业务停止处分的年月日和内容</t>
+  </si>
+  <si>
+    <t>宅建业者名簿记载内容7：</t>
+  </si>
+  <si>
+    <t>专任宅建士名字</t>
+  </si>
+  <si>
+    <t>宅建业者名簿不需要记录的内容：</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>暴力犯罪种类1：</t>
+  </si>
+  <si>
+    <t>伤害现场助势</t>
+  </si>
+  <si>
+    <t>暴力犯罪种类2：</t>
+  </si>
+  <si>
+    <t>暴行</t>
+  </si>
+  <si>
+    <t>暴力犯罪种类3：</t>
+  </si>
+  <si>
+    <t>凶器准备集合</t>
+  </si>
+  <si>
+    <t>暴力犯罪种类4：</t>
+  </si>
+  <si>
+    <t>胁迫</t>
+  </si>
+  <si>
+    <t>暴力犯罪种类5：</t>
+  </si>
+  <si>
+    <t>暴力团</t>
+  </si>
+  <si>
+    <t>暴力犯罪种类6：</t>
+  </si>
+  <si>
+    <t>不正手段获得免许</t>
+  </si>
+  <si>
+    <t>以下理由受到免许取消，免许取消日开始5年内不行的1：</t>
+  </si>
+  <si>
+    <t>业务停止的行为情状严重</t>
+  </si>
+  <si>
+    <t>以下理由受到免许取消，免许取消日开始5年内不行的2：</t>
+  </si>
+  <si>
+    <t>违反业务停止</t>
+  </si>
+  <si>
+    <t>以下理由受到免许取消，免许取消日开始5年内不行的3：</t>
+  </si>
+  <si>
+    <t>免许取消听闻公示日前或者紧急废业届出日前60天以内的法人役员</t>
+  </si>
+  <si>
+    <t>以下理由受到免许取消，免许取消日开始5年内不行的4：</t>
+  </si>
+  <si>
+    <t>宅建士不正受验，禁止</t>
+  </si>
+  <si>
+    <t>年内考试</t>
+  </si>
+  <si>
+    <t>不正手段登录</t>
+  </si>
+  <si>
+    <t>宅建士欠格事由，登陆消除处分5年内不行的1：</t>
+  </si>
+  <si>
+    <t>不正手段交付宅建士证</t>
+  </si>
+  <si>
+    <t>宅建士欠格事由，登陆消除处分5年内不行的2：</t>
+  </si>
+  <si>
+    <t>事务禁止处分行为，情状特别严重</t>
+  </si>
+  <si>
+    <t>宅建士欠格事由，登陆消除处分5年内不行的3：</t>
+  </si>
+  <si>
+    <t>违反事务禁止处分</t>
+  </si>
+  <si>
+    <t>宅建士欠格事由，登陆消除处分5年内不行的4：</t>
+  </si>
+  <si>
+    <t>宅建士欠格事由，登陆消除处分5年内不行的5：宅建士登录后没拿到证</t>
+  </si>
+  <si>
+    <t>进行了宅建士行为，情状特别严重</t>
+  </si>
+  <si>
+    <t>宅建士欠格事由，登陆消除处分5年内不行的6：宅建士登录后没拿到证</t>
+  </si>
+  <si>
+    <t>事务禁止最长</t>
+  </si>
+  <si>
+    <t>年</t>
+  </si>
+  <si>
+    <t>登录番号和年月日</t>
+  </si>
+  <si>
+    <t>宅建士资格登录簿内容1：</t>
+  </si>
+  <si>
+    <t>氏名</t>
+  </si>
+  <si>
+    <t>宅建士资格登录簿内容2：</t>
+  </si>
+  <si>
+    <t>生日和性别</t>
+  </si>
+  <si>
+    <t>宅建士资格登录簿内容3：</t>
+  </si>
+  <si>
+    <t>住所、本籍</t>
+  </si>
+  <si>
+    <t>宅建士资格登录簿内容4：</t>
+  </si>
+  <si>
+    <t>宅建业者的商号或名称、免许证番号</t>
+  </si>
+  <si>
+    <t>宅建士资格登录簿内容5：</t>
+  </si>
+  <si>
+    <t>考试合格年月日和番号</t>
+  </si>
+  <si>
+    <t>宅建士资格登录簿内容6：</t>
+  </si>
+  <si>
+    <t>指示处分、事务禁止处分的年月日和内容</t>
+  </si>
+  <si>
+    <t>宅建士资格登录簿内容7：</t>
+  </si>
+  <si>
+    <t>2.氏名</t>
+  </si>
+  <si>
+    <t>宅建士有变更要立刻申请的1：</t>
+  </si>
+  <si>
+    <t>4.住所、本籍</t>
+  </si>
+  <si>
+    <t>宅建士有变更要立刻申请的2：</t>
+  </si>
+  <si>
+    <t>5.宅建业者商号或名称、免许证番号</t>
+  </si>
+  <si>
+    <t>宅建士有变更要立刻申请的3：</t>
+  </si>
+  <si>
+    <t>转移登录</t>
+  </si>
+  <si>
+    <t>事务禁止期间不能做什么</t>
+  </si>
+  <si>
+    <t>变更登录</t>
+  </si>
+  <si>
+    <t>事务禁止期间能做什么</t>
+  </si>
+  <si>
+    <t>氏名、生年月日、住所</t>
+  </si>
+  <si>
+    <t>宅建士证记载内容1：</t>
+  </si>
+  <si>
+    <t>登录番号、登陆年月日</t>
+  </si>
+  <si>
+    <t>宅建士证记载内容2：</t>
+  </si>
+  <si>
+    <t>有效期截止日</t>
+  </si>
+  <si>
+    <t>宅建士证记载内容3：</t>
+  </si>
+  <si>
+    <t>交付年月日</t>
+  </si>
+  <si>
+    <t>宅建士证记载内容4：</t>
+  </si>
+  <si>
+    <t>失效</t>
+  </si>
+  <si>
+    <t>宅建士证要返纳1：</t>
+  </si>
+  <si>
+    <t>登录消除</t>
+  </si>
+  <si>
+    <t>宅建士证要返纳2：</t>
+  </si>
+  <si>
+    <t>找的旧的</t>
+  </si>
+  <si>
+    <t>宅建士证要返纳3：</t>
+  </si>
+  <si>
+    <t>营业保证金本店</t>
+  </si>
+  <si>
+    <t>万日元</t>
+  </si>
+  <si>
+    <t>营业保证金支店</t>
+  </si>
+  <si>
+    <t>国债</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>地方债政府保证债</t>
+  </si>
+  <si>
+    <t>其他国土交通省令有价债券</t>
+  </si>
+  <si>
+    <t>离本店最近的供讬所供讬然后届出</t>
+  </si>
+  <si>
+    <t>开新的支店需要：</t>
+  </si>
+  <si>
+    <t>才能开</t>
+  </si>
+  <si>
+    <t>收到免许权者通知的那天开始2周内</t>
+  </si>
+  <si>
+    <t>还付导致营业保证金不足要在：</t>
+  </si>
+  <si>
+    <t>（什么时间）补上</t>
+  </si>
+  <si>
+    <t>交钱那天开始2周内</t>
+  </si>
+  <si>
+    <t>营业保证金补上之后要在：</t>
+  </si>
+  <si>
+    <t>（什么时间）届出</t>
+  </si>
+  <si>
+    <t>破产</t>
+  </si>
+  <si>
+    <t>取回公告的情况1：</t>
+  </si>
+  <si>
+    <t>废业</t>
+  </si>
+  <si>
+    <t>取回公告的情况2：</t>
+  </si>
+  <si>
+    <t>关闭事务所</t>
+  </si>
+  <si>
+    <t>取回公告的情况3：</t>
+  </si>
+  <si>
+    <t>免许权者</t>
+  </si>
+  <si>
+    <t>公告时要向</t>
+  </si>
+  <si>
+    <t>届出</t>
+  </si>
+  <si>
+    <t>成为保证协会社员</t>
+  </si>
+  <si>
+    <t>不用公告的情况1：</t>
+  </si>
+  <si>
+    <t>本店转移</t>
+  </si>
+  <si>
+    <t>不用公告的情况2：</t>
+  </si>
+  <si>
+    <t>保证协会本店</t>
+  </si>
+  <si>
+    <t>保证协会支店</t>
+  </si>
+  <si>
+    <t>加入之前先交钱</t>
+  </si>
+  <si>
+    <t>加入保证协会需要：</t>
+  </si>
+  <si>
+    <t>2周内交钱</t>
+  </si>
+  <si>
+    <t>开新店需要：</t>
+  </si>
+  <si>
+    <t>1周</t>
+  </si>
+  <si>
+    <t>保证协会拿到钱后要在</t>
+  </si>
+  <si>
+    <t>（时间内）供讬</t>
+  </si>
+  <si>
+    <t>法务大臣及国土交通大臣指定的供讬所</t>
+  </si>
+  <si>
+    <t>保证协会拿到钱后要供讬到</t>
+  </si>
+  <si>
+    <t>（地点）</t>
+  </si>
+  <si>
+    <t>社员的免许权者</t>
+  </si>
+  <si>
+    <t>保证协会供讬后要向</t>
+  </si>
+  <si>
+    <t>（谁）届出</t>
+  </si>
+  <si>
+    <t>保证协会</t>
+  </si>
+  <si>
+    <t>保证协会赔钱需要：</t>
+  </si>
+  <si>
+    <t>（谁）认证</t>
+  </si>
+  <si>
+    <t>供讬所</t>
+  </si>
+  <si>
+    <t>认证后找：</t>
+  </si>
+  <si>
+    <t>（谁）拿钱</t>
+  </si>
+  <si>
+    <t>收到国土交通大臣的通知日开始2周内</t>
+  </si>
+  <si>
+    <t>保证协会赔完钱后不足要在：</t>
+  </si>
+  <si>
+    <t>收到纳付通知日开始2周内</t>
+  </si>
+  <si>
+    <t>保证协会让宅建业者补钱，宅建业者要在：</t>
+  </si>
+  <si>
+    <t>1周内</t>
+  </si>
+  <si>
+    <t>补不上会员地位没了，需要在：</t>
+  </si>
+  <si>
+    <t>（什么时间）供讬营业保证金</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>退出社员要公告吗</t>
+  </si>
+  <si>
+    <t>废弃事务所</t>
+  </si>
+  <si>
+    <t>什么情况不用公告</t>
+  </si>
+  <si>
+    <t>1个月内</t>
+  </si>
+  <si>
+    <t>保证金准备金，社员在收到通知日起的：</t>
+  </si>
+  <si>
+    <t>（什么时间）交</t>
+  </si>
+  <si>
+    <t>10天前</t>
+  </si>
+  <si>
+    <t>设置能申请和契约的案内所需要：</t>
+  </si>
+  <si>
+    <t>免许权者和案内所所在地都道府县知事</t>
+  </si>
+  <si>
+    <t>向谁届出</t>
+  </si>
+  <si>
+    <t>2周内</t>
+  </si>
+  <si>
+    <t>宅建士人数不足是需要在</t>
+  </si>
+  <si>
+    <t>30天内届出</t>
+  </si>
+  <si>
+    <t>人员变动需要</t>
+  </si>
+  <si>
+    <t>（什么时间做什么）</t>
+  </si>
+  <si>
+    <t>事务所和案内所</t>
+  </si>
+  <si>
+    <t>标识需要在什么地方揭示</t>
+  </si>
+  <si>
+    <t>标识共通记载事项1：</t>
+  </si>
+  <si>
+    <t>标识共通记载事项2：</t>
+  </si>
+  <si>
+    <t>标识共通记载事项3：</t>
+  </si>
+  <si>
+    <t>代表者氏名</t>
+  </si>
+  <si>
+    <t>标识共通记载事项4：</t>
+  </si>
+  <si>
+    <t>本店所在地</t>
+  </si>
+  <si>
+    <t>标识共通记载事项5：</t>
+  </si>
+  <si>
+    <t>标识个别记载事项，事务所1：</t>
+  </si>
+  <si>
+    <t>专任宅建士人数</t>
+  </si>
+  <si>
+    <t>标识个别记载事项，事务所2：</t>
+  </si>
+  <si>
+    <t>土地非定着要写适用冷静制度</t>
+  </si>
+  <si>
+    <t>标识个别记载事项，申请·契约案内所：</t>
+  </si>
+  <si>
+    <t>冷静制度适用</t>
+  </si>
+  <si>
+    <t>标识个别记载事项，非申请·契约案内所：</t>
+  </si>
+  <si>
+    <t>把卖主的商号或名称以及免许证番号也写出来</t>
+  </si>
+  <si>
+    <t>案内所如果是代理或媒介其他宅建业者一团宅地建物的分让，还要怎么样</t>
+  </si>
+  <si>
+    <t>各事务所</t>
+  </si>
+  <si>
+    <t>账本什么地方要有：</t>
+  </si>
+  <si>
+    <t>封账后保留5年，宅建业者卖自己的房子要保留10年</t>
+  </si>
+  <si>
+    <t>账本保留多长时间：</t>
+  </si>
+  <si>
+    <t>从业者名簿什么地方要有：</t>
+  </si>
+  <si>
+    <t>最后记录之日开始10年</t>
+  </si>
+  <si>
+    <t>从业者名簿保留多长时间：</t>
+  </si>
+  <si>
+    <t>主要职务内容</t>
+  </si>
+  <si>
+    <t>从业者名簿记录内容1：</t>
+  </si>
+  <si>
+    <t>入职年月日</t>
+  </si>
+  <si>
+    <t>从业者名簿记录内容2：</t>
+  </si>
+  <si>
+    <t>离职年月日</t>
+  </si>
+  <si>
+    <t>从业者名簿记录内容3：</t>
+  </si>
+  <si>
+    <t>是否是宅建士</t>
+  </si>
+  <si>
+    <t>从业者名簿记录内容4：</t>
+  </si>
+  <si>
+    <t>报酬额什么地方要有：</t>
+  </si>
+  <si>
+    <t>3个月，不能更新</t>
+  </si>
+  <si>
+    <t>媒介契约有效期以及是否能更新：</t>
+  </si>
+  <si>
+    <t>1周1次</t>
+  </si>
+  <si>
+    <t>汇报频率，专属专任：</t>
+  </si>
+  <si>
+    <t>2周1次</t>
+  </si>
+  <si>
+    <t>汇报频率，专任：</t>
+  </si>
+  <si>
+    <t>专任7天，专属专任5天，不包含工作日</t>
+  </si>
+  <si>
+    <t>多少天内登录指定流通机构：</t>
+  </si>
+  <si>
+    <t>宅地建物所在、规模、形质，买卖价格/交换评价额</t>
+  </si>
+  <si>
+    <t>登陆内容1：</t>
+  </si>
+  <si>
+    <t>宅地建物相关都市计划法限制</t>
+  </si>
+  <si>
+    <t>登陆内容2：</t>
+  </si>
+  <si>
+    <t>专属专任的话注明</t>
+  </si>
+  <si>
+    <t>登陆内容3：</t>
+  </si>
+  <si>
+    <t>宅地建物取引申请受付状况</t>
+  </si>
+  <si>
+    <t>登陆内容4：</t>
+  </si>
+  <si>
+    <t>登录番号</t>
+  </si>
+  <si>
+    <t>媒介契约成立后通知事项1：</t>
+  </si>
+  <si>
+    <t>宅地建物交易价格</t>
+  </si>
+  <si>
+    <t>媒介契约成立后通知事项2：</t>
+  </si>
+  <si>
+    <t>买卖交换契约成立年月日</t>
+  </si>
+  <si>
+    <t>媒介契约成立后通知事项3：</t>
+  </si>
+  <si>
+    <t>买卖交换需要，赁借不用</t>
+  </si>
+  <si>
+    <t>买卖交换和赁借媒介契约缔结时，要立刻交付书面？</t>
+  </si>
+  <si>
+    <t>能特定宅地建物的必要表示</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容1：</t>
+  </si>
+  <si>
+    <t>买卖价格/交换评价额（价格意见要明示根据，可以口头）</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容2：</t>
+  </si>
+  <si>
+    <t>媒介契约种类</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容3：</t>
+  </si>
+  <si>
+    <t>报酬</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容4：</t>
+  </si>
+  <si>
+    <t>有效期和解除事项</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容5：</t>
+  </si>
+  <si>
+    <t>违反契约的措施</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容6：</t>
+  </si>
+  <si>
+    <t>是否基于标准媒介约款</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容7：</t>
+  </si>
+  <si>
+    <t>指定流通机构登录事项（一般也不能省略）</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容8：</t>
+  </si>
+  <si>
+    <t>既存建物，依赖者建物状况调查实施斡旋（标准媒介约款时没有的话要记录理由）</t>
+  </si>
+  <si>
+    <t>媒介契约书面记载内容9：</t>
+  </si>
+  <si>
+    <t>所在、规模、形质</t>
+  </si>
+  <si>
+    <t>规制对象广告内容1：</t>
+  </si>
+  <si>
+    <t>现在将来利用限制、环境、交通及其他利便</t>
+  </si>
+  <si>
+    <t>规制对象广告内容2：</t>
+  </si>
+  <si>
+    <t>代金、借赁等对价的额、支付方法</t>
+  </si>
+  <si>
+    <t>规制对象广告内容3：</t>
+  </si>
+  <si>
+    <t>代金、交换差金相关金钱贷借的斡旋</t>
+  </si>
+  <si>
+    <t>规制对象广告内容4：</t>
+  </si>
+  <si>
+    <t>未完成物件获得开发许可或建筑确认前，不能广告也不能契约</t>
+  </si>
+  <si>
+    <t>广告开始时期：</t>
+  </si>
+  <si>
+    <t>贷借可以契约不能广告</t>
+  </si>
+  <si>
+    <t>例外：</t>
+  </si>
+  <si>
+    <t>契约前</t>
+  </si>
+  <si>
+    <t>重要事项要在</t>
+  </si>
+  <si>
+    <t>（什么时候）进行</t>
+  </si>
+  <si>
+    <t>买主或者借主</t>
+  </si>
+  <si>
+    <t>重要事项要向</t>
+  </si>
+  <si>
+    <t>（谁）进行</t>
+  </si>
+  <si>
+    <t>书面交付和说明</t>
+  </si>
+  <si>
+    <t>重要事项要做什么：</t>
+  </si>
+  <si>
+    <t>10万日元</t>
+  </si>
+  <si>
+    <t>重要事项说明没提示宅建士证要罚多少钱</t>
+  </si>
+  <si>
+    <t>登记权利种类·内容</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关1：</t>
+  </si>
+  <si>
+    <t>法令上的限制（租房不用说建蔽率、容积率之类的）</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关2：</t>
+  </si>
+  <si>
+    <t>私道负担（没有的话也得说一句没有，租房不用说）</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关3：</t>
+  </si>
+  <si>
+    <t>电气、瓦斯、水道供给设施，排水设施整备状况</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关4：</t>
+  </si>
+  <si>
+    <t>既存建物，建物状况调查结果概要（实施1年内公寓等2年），维持保全状况书类保存状况（租房不用）</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关5：</t>
+  </si>
+  <si>
+    <t>未完成物件完成时的形状构造等</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关6：</t>
+  </si>
+  <si>
+    <t>造成宅地是否在防灾区域内</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关7：</t>
+  </si>
+  <si>
+    <t>是否在土砂灾害警戒区域内</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关8：</t>
+  </si>
+  <si>
+    <t>是否在津波灾害境界区域内</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关9：</t>
+  </si>
+  <si>
+    <t>基于水害地图，交易对象宅地建物所在地</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关10：</t>
+  </si>
+  <si>
+    <t>石棉适用调查内容</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关11：</t>
+  </si>
+  <si>
+    <t>耐震诊断的内容，昭和56年（1981）6月1日前</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关12：</t>
+  </si>
+  <si>
+    <t>接受住宅性能评价的新筑住宅（仅买房，仅新房）</t>
+  </si>
+  <si>
+    <t>35条内容，物件相关13：</t>
+  </si>
+  <si>
+    <t>敷地权利种类·内容</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有1：</t>
+  </si>
+  <si>
+    <t>共用部分规制</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有2：</t>
+  </si>
+  <si>
+    <t>专有部分用途及利用限制（租房得说）</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有3：</t>
+  </si>
+  <si>
+    <t>专用使用权</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有4：</t>
+  </si>
+  <si>
+    <t>建物所有者负担费用特定者减免</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有5：</t>
+  </si>
+  <si>
+    <t>修缮积立金内容、已积立金额</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有6：</t>
+  </si>
+  <si>
+    <t>通常管理费用金额</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有7：</t>
+  </si>
+  <si>
+    <t>管理委托方的氏名、住所（租房得说）</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有8：</t>
+  </si>
+  <si>
+    <t>建物维持修缮实施状况</t>
+  </si>
+  <si>
+    <t>35条内容，区分所有9：</t>
+  </si>
+  <si>
+    <t>代金、交换差金、借赁以外授受的金钱（手付金、敷金、礼金等）</t>
+  </si>
+  <si>
+    <t>35条内容，交易相关1：</t>
+  </si>
+  <si>
+    <t>契约的届出</t>
+  </si>
+  <si>
+    <t>35条内容，交易相关2：</t>
+  </si>
+  <si>
+    <t>损害赔偿额的预定、违约金</t>
+  </si>
+  <si>
+    <t>35条内容，交易相关3：</t>
+  </si>
+  <si>
+    <t>手付金保全措施概要（租房不用）</t>
+  </si>
+  <si>
+    <t>35条内容，交易相关4：</t>
+  </si>
+  <si>
+    <t>支付金、預り金有没有保全措施，有的话讲概要，支付金定义如下：不满50万、没讲保全措施的手付金、卖主·交换当事人宅建业者登记以后受领的、不包含报酬</t>
+  </si>
+  <si>
+    <t>35条内容，交易相关5：</t>
+  </si>
+  <si>
+    <t>代金、交换差金相关贷款斡旋内容、贷款不成立时的措施（租房不用）</t>
+  </si>
+  <si>
+    <t>35条内容，交易相关6：</t>
+  </si>
+  <si>
+    <t>一定担保责任（租房不用），“合同约定卖方不承担契约不适合责任”不用说明，担保责任履行措施概要要说明（没有也要说没有）</t>
+  </si>
+  <si>
+    <t>35条内容，交易相关7：</t>
+  </si>
+  <si>
+    <t>台所、浴室、便所（只租房说）</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关1：</t>
+  </si>
+  <si>
+    <t>契约期间·更新</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关2：</t>
+  </si>
+  <si>
+    <t>用途和利用限制</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关3：</t>
+  </si>
+  <si>
+    <t>管理委托方氏名和住所</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关4：</t>
+  </si>
+  <si>
+    <t>敷金和其他精算金钱</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关5：</t>
+  </si>
+  <si>
+    <t>定期借地权</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关6：</t>
+  </si>
+  <si>
+    <t>定期建物赁贷借</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关7：</t>
+  </si>
+  <si>
+    <t>高龄居住安定确保终身建物赁贷借（直到借主死）</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关8：</t>
+  </si>
+  <si>
+    <t>契约结束时宅地建物取坏</t>
+  </si>
+  <si>
+    <t>35条内容，赁贷相关9：</t>
+  </si>
+  <si>
+    <t>当事者氏名和住所</t>
+  </si>
+  <si>
+    <t>37条内容，必须要有1：</t>
+  </si>
+  <si>
+    <t>宅地建物特定必要表示</t>
+  </si>
+  <si>
+    <t>37条内容，必须要有2：</t>
+  </si>
+  <si>
+    <t>代金·交换差金·租金额·支付时期·支付方法</t>
+  </si>
+  <si>
+    <t>37条内容，必须要有3：</t>
+  </si>
+  <si>
+    <t>引渡时期</t>
+  </si>
+  <si>
+    <t>37条内容，必须要有4：</t>
+  </si>
+  <si>
+    <t>转移登记申请时期</t>
+  </si>
+  <si>
+    <t>37条内容，必须要有5：</t>
+  </si>
+  <si>
+    <t>既存建筑物构造耐力</t>
+  </si>
+  <si>
+    <t>37条内容，必须要有6：</t>
+  </si>
+  <si>
+    <t>代金·交换差金·租金以外金钱授受（手付·敷金·礼金之类）</t>
+  </si>
+  <si>
+    <t>37条内容，定了要记1：</t>
+  </si>
+  <si>
+    <t>契约解除</t>
+  </si>
+  <si>
+    <t>37条内容，定了要记2：</t>
+  </si>
+  <si>
+    <t>损害赔偿额预定·违约金</t>
+  </si>
+  <si>
+    <t>37条内容，定了要记3：</t>
+  </si>
+  <si>
+    <t>天灾损害负担</t>
+  </si>
+  <si>
+    <t>37条内容，定了要记4：</t>
+  </si>
+  <si>
+    <t>代金·交换差金贷款斡旋</t>
+  </si>
+  <si>
+    <t>37条内容，定了要记5：</t>
+  </si>
+  <si>
+    <t>一定的担保责任</t>
+  </si>
+  <si>
+    <t>37条内容，定了要记6：</t>
+  </si>
+  <si>
+    <t>租税公课</t>
+  </si>
+  <si>
+    <t>37条内容，定了要记7：</t>
+  </si>
+  <si>
+    <t>登记</t>
+  </si>
+  <si>
+    <t>禁止不当履行延迟1：</t>
+  </si>
+  <si>
+    <t>引渡</t>
+  </si>
+  <si>
+    <t>禁止不当履行延迟2：</t>
+  </si>
+  <si>
+    <t>代金支付</t>
+  </si>
+  <si>
+    <t>禁止不当履行延迟3：</t>
+  </si>
+  <si>
+    <t>不能</t>
+  </si>
+  <si>
+    <t>宅建业者是否能以行为能力限制取消？</t>
+  </si>
+  <si>
+    <t>告知之日起8天内可以，过了不行</t>
+  </si>
+  <si>
+    <t>冷静制度多少天内可以？</t>
+  </si>
+  <si>
+    <t>引渡且支付全款</t>
+  </si>
+  <si>
+    <t>冷静制度什么情况就不行了</t>
+  </si>
+  <si>
+    <t>发出</t>
+  </si>
+  <si>
+    <t>以什么时间判断？发出？收到？</t>
+  </si>
+  <si>
+    <t>引渡开始2年以上</t>
+  </si>
+  <si>
+    <t>宅建业法规定的担保责任，什么样的特约有效</t>
+  </si>
+  <si>
+    <t>（什么时间开始多长时间内）</t>
+  </si>
+  <si>
+    <t>2/10</t>
+  </si>
+  <si>
+    <t>损害赔偿额或违约金先定的话不超过</t>
+  </si>
+  <si>
+    <t>比例</t>
+  </si>
+  <si>
+    <t>实际损失额</t>
+  </si>
+  <si>
+    <t>没定的话，赔多少？</t>
+  </si>
+  <si>
+    <t>手付金，宅建业法规定不超过</t>
+  </si>
+  <si>
+    <t>银行等</t>
+  </si>
+  <si>
+    <t>未完成物件保全措施1：</t>
+  </si>
+  <si>
+    <t>保险会社</t>
+  </si>
+  <si>
+    <t>未完成物件保全措施2：</t>
+  </si>
+  <si>
+    <t>完成物件保全措施1：</t>
+  </si>
+  <si>
+    <t>完成物件保全措施2：</t>
+  </si>
+  <si>
+    <t>指定保管机关（保证协会）</t>
+  </si>
+  <si>
+    <t>完成物件保全措施3：</t>
+  </si>
+  <si>
+    <t>买主已经所有权转移登记了</t>
+  </si>
+  <si>
+    <t>不需要保全措施：</t>
+  </si>
+  <si>
+    <t>代金 5%（含税）以下且1000万以下</t>
+  </si>
+  <si>
+    <t>未完成物件，不需要保全措施的金额：</t>
+  </si>
+  <si>
+    <t>代金 10% 以下且1000万以下</t>
+  </si>
+  <si>
+    <t>完成物件，不需要保全措施的金额：</t>
+  </si>
+  <si>
+    <t>1年，2次</t>
+  </si>
+  <si>
+    <t>割赋贩售分期要在引渡后多长时间以上分几次才行</t>
+  </si>
+  <si>
+    <t>买主没交钱，要催告多少天：</t>
+  </si>
+  <si>
+    <t>3/10</t>
+  </si>
+  <si>
+    <t>所有权留保：收到多少比例的房款就不行了</t>
+  </si>
+  <si>
+    <t>税率10%（消费税率7.8%，地方消费税率2.2%）</t>
+  </si>
+  <si>
+    <t>报酬税率：总税率，消费税率和地方消费税率分别是多少？</t>
+  </si>
+  <si>
+    <t>土地、居住用贷借</t>
+  </si>
+  <si>
+    <t>什么不课税</t>
+  </si>
+  <si>
+    <t>1.1和1.04</t>
+  </si>
+  <si>
+    <t>报酬税额，课税业者和非课税业者分别是多少：</t>
+  </si>
+  <si>
+    <t>买卖交换报酬限度，200万以内：</t>
+  </si>
+  <si>
+    <t>4%+2</t>
+  </si>
+  <si>
+    <t>买卖交换报酬限度，200万~400万：</t>
+  </si>
+  <si>
+    <t>3%+6</t>
+  </si>
+  <si>
+    <t>买卖交换报酬限度，400万以上：</t>
+  </si>
+  <si>
+    <t>媒介是</t>
+  </si>
+  <si>
+    <t>倍</t>
+  </si>
+  <si>
+    <t>代理是</t>
+  </si>
+  <si>
+    <t>33万，代理2倍</t>
+  </si>
+  <si>
+    <t>800万以下宅地建物不管使用状态，最多多少钱，代理的话呢？</t>
+  </si>
+  <si>
+    <t>1个月租金</t>
+  </si>
+  <si>
+    <t>赁借的报酬额</t>
+  </si>
+  <si>
+    <t>半个月租金</t>
+  </si>
+  <si>
+    <t>没有允许的话，最多从借主收多少</t>
+  </si>
+  <si>
+    <t>2.2倍</t>
+  </si>
+  <si>
+    <t>长期空家多少倍</t>
+  </si>
+  <si>
+    <t>业务相关违反宅建业法以外法令，宅建业者不适当</t>
+  </si>
+  <si>
+    <t>宅建业者【指示处分】事由1：</t>
+  </si>
+  <si>
+    <t>宅建士受指示处分，归责于宅建业者</t>
+  </si>
+  <si>
+    <t>宅建业者【指示处分】事由2：</t>
+  </si>
+  <si>
+    <t>业务相关对交易关系者造成损害或可能造成损害</t>
+  </si>
+  <si>
+    <t>宅建业者【指示处分】事由3：</t>
+  </si>
+  <si>
+    <t>违反宅建业法</t>
+  </si>
+  <si>
+    <t>宅建业者【指示处分】事由4：</t>
+  </si>
+  <si>
+    <t>同指示处分1</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由1：</t>
+  </si>
+  <si>
+    <t>同指示处分2</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由2：</t>
+  </si>
+  <si>
+    <t>违反指示处分</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由3：</t>
+  </si>
+  <si>
+    <t>宅建业相关不正或显著不正行为</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由4：</t>
+  </si>
+  <si>
+    <t>违反宅建业法一定规定</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5：</t>
+  </si>
+  <si>
+    <t>夸大广告</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定1：</t>
+  </si>
+  <si>
+    <t>没明示取引态样</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定2：</t>
+  </si>
+  <si>
+    <t>没交付34条</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定3：</t>
+  </si>
+  <si>
+    <t>没交付或说明35条</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定4：</t>
+  </si>
+  <si>
+    <t>没交付37条</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定5：</t>
+  </si>
+  <si>
+    <t>超过报酬额</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定6：</t>
+  </si>
+  <si>
+    <t>没带从业证</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定7：</t>
+  </si>
+  <si>
+    <t>违反守秘义务</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定8：</t>
+  </si>
+  <si>
+    <t>违反专任宅建士设置</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定9：</t>
+  </si>
+  <si>
+    <t>违反营业保证金或保证协会</t>
+  </si>
+  <si>
+    <t>宅建业者【事务停止处分】事由5的规定10：</t>
+  </si>
+  <si>
+    <t>保证金供讬没届出</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【可以】取消的1：</t>
+  </si>
+  <si>
+    <t>宅建业者所在地不明（免许权者不知道所在会进行公告，公告日开始30天内宅建业者没申出）</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【可以】取消的2：</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的1：</t>
+  </si>
+  <si>
+    <t>有业务停止处分行为情状特别严重</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的2：</t>
+  </si>
+  <si>
+    <t>违反业务停止处分</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的3：</t>
+  </si>
+  <si>
+    <t>心身故障和破产者</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的4：</t>
+  </si>
+  <si>
+    <t>禁锢以上刑</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的5：</t>
+  </si>
+  <si>
+    <t>违法宅建业法、暴力犯罪、背任罪罚金以上</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的6：</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的7：</t>
+  </si>
+  <si>
+    <t>未成年法定代理人欠格事由</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的8：</t>
+  </si>
+  <si>
+    <t>法人的役员、政令使用人欠格事由</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的9：</t>
+  </si>
+  <si>
+    <t>获得免许1年以内没开始事业的或者1年以上休业的</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的10：</t>
+  </si>
+  <si>
+    <t>发生免许更换但是没获得新免许的</t>
+  </si>
+  <si>
+    <t>宅建业者【免许取消处分】事由之【必须】取消的11：</t>
+  </si>
+  <si>
+    <t>违反35条说明</t>
+  </si>
+  <si>
+    <t>国土交通大臣对宅建业者进行监督处分前要和内阁总理大臣协议的1：</t>
+  </si>
+  <si>
+    <t>违反37条交付</t>
+  </si>
+  <si>
+    <t>国土交通大臣对宅建业者进行监督处分前要和内阁总理大臣协议的2：</t>
+  </si>
+  <si>
+    <t>国土交通大臣对宅建业者进行监督处分前要和内阁总理大臣协议的3：</t>
+  </si>
+  <si>
+    <t>取引态样未明示</t>
+  </si>
+  <si>
+    <t>国土交通大臣对宅建业者进行监督处分前要和内阁总理大臣协议的4：</t>
+  </si>
+  <si>
+    <t>国土交通大臣对宅建业者进行监督处分前要和内阁总理大臣协议的5：</t>
+  </si>
+  <si>
+    <t>在两个事务所做专任宅建士</t>
+  </si>
+  <si>
+    <t>宅建士【指示】事由1：</t>
+  </si>
+  <si>
+    <t>出借或使用他人名义</t>
+  </si>
+  <si>
+    <t>宅建士【指示】事由2：</t>
+  </si>
+  <si>
+    <t>宅建士业务相关不正或显著不正行为</t>
+  </si>
+  <si>
+    <t>宅建士【指示】事由3：</t>
+  </si>
+  <si>
+    <t>指示处分对象事由</t>
+  </si>
+  <si>
+    <t>宅建士【事务禁止】事由1：</t>
+  </si>
+  <si>
+    <t>不服从指示处分</t>
+  </si>
+  <si>
+    <t>宅建士【事务禁止】事由2：</t>
+  </si>
+  <si>
+    <t>登录欠格事由</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【宅建士】的1：</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【宅建士】的2：</t>
+  </si>
+  <si>
+    <t>不正手段拿宅建士证</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【宅建士】的3：</t>
+  </si>
+  <si>
+    <t>事务禁止行为情状特别严重</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【宅建士】的4：</t>
+  </si>
+  <si>
+    <t>违反事务禁止</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【宅建士】的5：</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【登录没拿证】的1：</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【登录没拿证】的2：</t>
+  </si>
+  <si>
+    <t>进行宅建士行为情状特别严重</t>
+  </si>
+  <si>
+    <t>【登录消除】事由，【登录没拿证】的3：</t>
+  </si>
+  <si>
+    <t>罚【3年】和【300万】的1：</t>
+  </si>
+  <si>
+    <t>无免许进行事业</t>
+  </si>
+  <si>
+    <t>罚【3年】和【300万】的2：</t>
+  </si>
+  <si>
+    <t>出借名义</t>
+  </si>
+  <si>
+    <t>罚【3年】和【300万】的3：</t>
+  </si>
+  <si>
+    <t>罚【3年】和【300万】的4：</t>
+  </si>
+  <si>
+    <t>为了契约隐瞒事实</t>
+  </si>
+  <si>
+    <t>罚【2年】和【200万】的：</t>
+  </si>
+  <si>
+    <t>不正高额报酬</t>
+  </si>
+  <si>
+    <t>罚【1年】和【100万】的：</t>
+  </si>
+  <si>
+    <t>没供讬营业保证金就开始事业</t>
+  </si>
+  <si>
+    <t>罚【6个月】和【100万】的1：</t>
+  </si>
+  <si>
+    <t>罚【6个月】和【100万】的2：</t>
+  </si>
+  <si>
+    <t>不当履行延迟</t>
+  </si>
+  <si>
+    <t>罚【6个月】和【100万】的3：</t>
+  </si>
+  <si>
+    <t>手付贷付</t>
+  </si>
+  <si>
+    <t>罚【6个月】和【100万】的4：</t>
+  </si>
+  <si>
+    <t>无免许进行表示和广告</t>
+  </si>
+  <si>
+    <t>罚【100万】的1：</t>
+  </si>
+  <si>
+    <t>出借名义给他人做表示和广告</t>
+  </si>
+  <si>
+    <t>罚【100万】的2：</t>
+  </si>
+  <si>
+    <t>罚【100万】的3：</t>
+  </si>
+  <si>
+    <t>超过限度额报酬</t>
+  </si>
+  <si>
+    <t>罚【100万】的4：</t>
+  </si>
+  <si>
+    <t>变更没届出或虚假届出</t>
+  </si>
+  <si>
+    <t>罚【50万】的1：</t>
+  </si>
+  <si>
+    <t>罚【50万】的2：</t>
+  </si>
+  <si>
+    <t>事务所没揭示报酬</t>
+  </si>
+  <si>
+    <t>罚【50万】的3：</t>
+  </si>
+  <si>
+    <t>没带从业者证</t>
+  </si>
+  <si>
+    <t>罚【50万】的4：</t>
+  </si>
+  <si>
+    <t>没有标识</t>
+  </si>
+  <si>
+    <t>罚【50万】的5：</t>
+  </si>
+  <si>
+    <t>罚【50万】的6：</t>
+  </si>
+  <si>
+    <t>没账本或从业者名簿</t>
+  </si>
+  <si>
+    <t>罚【50万】的7：</t>
+  </si>
+  <si>
+    <t>没记载或虚假记载</t>
+  </si>
+  <si>
+    <t>罚【50万】的8：</t>
+  </si>
+  <si>
+    <t>没有业务报告或虚假业务报告</t>
+  </si>
+  <si>
+    <t>罚【50万】的9：</t>
+  </si>
+  <si>
+    <t>妨碍国土交通大臣和知事检查</t>
+  </si>
+  <si>
+    <t>罚【50万】的10：</t>
+  </si>
+  <si>
+    <t>未返纳</t>
+  </si>
+  <si>
+    <t>罚【10万】的1：</t>
+  </si>
+  <si>
+    <t>未提出</t>
+  </si>
+  <si>
+    <t>罚【10万】的2：</t>
+  </si>
+  <si>
+    <t>35条说明时未提示</t>
+  </si>
+  <si>
+    <t>罚【10万】的3：</t>
+  </si>
+  <si>
+    <t>3周内</t>
+  </si>
+  <si>
+    <t>住宅瑕疵担保，基准日开始的</t>
+  </si>
+  <si>
+    <t>（时间）供讬</t>
+  </si>
+  <si>
+    <t>供讬多少年的</t>
+  </si>
+  <si>
+    <t>多少平米以下二合一</t>
+  </si>
+  <si>
+    <t>2000万</t>
+  </si>
+  <si>
+    <t>住宅瑕疵担保，保险的话最低多少钱</t>
+  </si>
+  <si>
+    <t>基准日翌日的50天后</t>
+  </si>
+  <si>
+    <t>没届出的话，从什么时候起就不能卖自己的新房了？</t>
+  </si>
+  <si>
+    <t>不法行为造成的损害赔偿请求、继承、遗赠</t>
+  </si>
+  <si>
+    <t>胎儿有什么权利：</t>
+  </si>
+  <si>
+    <t>（3个）</t>
+  </si>
+  <si>
+    <t>权利关系</t>
+  </si>
+  <si>
+    <t>任意，不管善意恶意</t>
+  </si>
+  <si>
+    <t>因【未成年】取消，可以和什么样的第三者对抗？</t>
+  </si>
+  <si>
+    <t>因【后见】未成年取消，可以和什么样的第三者对抗？</t>
+  </si>
+  <si>
+    <t>成年被后见人居住用建物·敷地的卖却、赁贷、赁贷借解除或抵当权设定</t>
+  </si>
+  <si>
+    <t>后见人什么行为需要家庭裁判所许可？</t>
+  </si>
+  <si>
+    <t>【低层】住宅...【良好】住居环境保护</t>
+  </si>
+  <si>
+    <t>第一种低层住居专用地域定义：</t>
+  </si>
+  <si>
+    <t>法令</t>
+  </si>
+  <si>
+    <t>【主】...【低层】住宅...【良好】住居环境保护</t>
+  </si>
+  <si>
+    <t>第二种低层住居专用地域定义：</t>
+  </si>
+  <si>
+    <t>【农业】利便增进...【调和】低层住宅...【良好】住居环境保护</t>
+  </si>
+  <si>
+    <t>田园住居地域定义：</t>
+  </si>
+  <si>
+    <t>【中高层】住宅...【良好】住居环境保护</t>
+  </si>
+  <si>
+    <t>第一种中高层住居专用地域定义：</t>
+  </si>
+  <si>
+    <t>【主】...【中高层】住宅...【良好】住居环境保护</t>
+  </si>
+  <si>
+    <t>第二种中高层住居专用地域定义：</t>
+  </si>
+  <si>
+    <t>【住居】环境保护</t>
+  </si>
+  <si>
+    <t>第一种住居地域定义：</t>
+  </si>
+  <si>
+    <t>【主】...【住居】环境保护</t>
+  </si>
+  <si>
+    <t>第二种住居地域定义：</t>
+  </si>
+  <si>
+    <t>【道路】沿道..地域特性...【业务利便】增进...【调和】...【住居】环境保护</t>
+  </si>
+  <si>
+    <t>准住居地域定义：</t>
+  </si>
+  <si>
+    <t>【近邻】住宅地住民【日用品】供给主内容...商业其他业务利便增进</t>
+  </si>
+  <si>
+    <t>近邻商业地域定义：</t>
+  </si>
+  <si>
+    <t>【主】...【商业】其他业务利便增进</t>
+  </si>
+  <si>
+    <t>商业地域定义：</t>
+  </si>
+  <si>
+    <t>【主】...【环境恶化】.....【工业】利便增进</t>
+  </si>
+  <si>
+    <t>准工业地域定义：</t>
+  </si>
+  <si>
+    <t>【主】...【工业】利便增进</t>
+  </si>
+  <si>
+    <t>工业地域定义：</t>
+  </si>
+  <si>
+    <t>【工业】利便增进</t>
+  </si>
+  <si>
+    <t>工业专用地域定义：</t>
+  </si>
+  <si>
+    <t>【所有】容积率，【商业以外】建蔽率，【一二低田园】高度上限</t>
+  </si>
+  <si>
+    <t>用途地域【必定】事项：</t>
+  </si>
+  <si>
+    <t>【所有】敷地面积下限，【一二低田园】外壁后退距离限度</t>
+  </si>
+  <si>
+    <t>用途地域【可定】事项：</t>
+  </si>
+  <si>
+    <t>特别用途地域、高度地区、高度利用地区、高层住居诱导地区、特例容积率适用地区、居住环境向上用途诱导地区</t>
+  </si>
+  <si>
+    <t>【辅助用途地域】只能在【用途地域内】定的：</t>
+  </si>
+  <si>
+    <t>特定街区、防火准防火、景观、风致</t>
+  </si>
+  <si>
+    <t>【辅助用途地域】可在【用途地域内或外】定的：</t>
+  </si>
+  <si>
+    <t>特定用途限制地域</t>
+  </si>
+  <si>
+    <t>【辅助用途地域】只能在【用途地域外】定的：</t>
+  </si>
+  <si>
+    <t>特性...土地利用增进...环境保护...补完...</t>
+  </si>
+  <si>
+    <t>【特别用途地域】定义：</t>
+  </si>
+  <si>
+    <t>建筑物的【高】的【最高】限度或者【最低】限度</t>
+  </si>
+  <si>
+    <t>【高度地区】定义：</t>
+  </si>
+  <si>
+    <t>土地合理健全高度利用都市机能更新，【容积率|高低】【建蔽率|高】【建筑面积|低】【壁面位置】</t>
+  </si>
+  <si>
+    <t>住居用途适正分配...高层住宅建设诱导...【一|二|准|近邻|准工】容积率40或50的，定【容积率|高】【建蔽率|高】【敷地面积|低】</t>
+  </si>
+  <si>
+    <t>【高层住居诱导】定义：</t>
+  </si>
+  <si>
+    <t>【一二中高|一|二|准|近邻|商|准工|工】适正配置...公共设施...容积率限度...未利用</t>
+  </si>
+  <si>
+    <t>【特定容积率】定义：</t>
+  </si>
+  <si>
+    <t>立地适正计划...病院店铺等日常生活必要设施...</t>
+  </si>
+  <si>
+    <t>【居住环境向上】定义：</t>
+  </si>
+  <si>
+    <t>市街地整备改善，定【容积率】【高度|高】【壁面位置】</t>
+  </si>
+  <si>
+    <t>【特定街区】定义：</t>
+  </si>
+  <si>
+    <t>火灾危险防除</t>
+  </si>
+  <si>
+    <t>【防火·准防火】定义：</t>
+  </si>
+  <si>
+    <t>良好景观</t>
+  </si>
+  <si>
+    <t>【景观】定义：</t>
+  </si>
+  <si>
+    <t>都市风致（自然美）</t>
+  </si>
+  <si>
+    <t>【风致】定义：</t>
+  </si>
+  <si>
+    <t>未定用途地域...</t>
+  </si>
+  <si>
+    <t>【特定用途限制】定义：</t>
+  </si>
+  <si>
+    <t>特别用途地区、高度地区、景观、风致、特定用途限制</t>
+  </si>
+  <si>
+    <t>【准都市】可以定的辅助用途地域有哪些：</t>
+  </si>
+  <si>
+    <t>道路、下水道、公园</t>
+  </si>
+  <si>
+    <t>市街化和非线引必定的【都市设施】有：</t>
+  </si>
+  <si>
+    <t>义务教育设施</t>
+  </si>
+  <si>
+    <t>住居系必定的【都市设施】有：</t>
+  </si>
+  <si>
+    <t>土地合理健全高度利用都市机能增进</t>
+  </si>
+  <si>
+    <t>地区计划的【再开发等促进区】定义：</t>
+  </si>
+  <si>
+    <t>剧场店铺等大规模建筑物</t>
+  </si>
+  <si>
+    <t>地区计划的【开发整备促进区】定义：</t>
+  </si>
+  <si>
+    <t>土地区划形质变更、建筑物的建筑、工作物的建设</t>
+  </si>
+  <si>
+    <t>一定地区计划区域内有什么行为需要【届出】：</t>
+  </si>
+  <si>
+    <t>着手日前30天前</t>
+  </si>
+  <si>
+    <t>一定地区计划区域的行为要什么时候届出？</t>
+  </si>
+  <si>
+    <t>市町村长</t>
+  </si>
+  <si>
+    <t>一定地区计划区域的行为向谁届出？</t>
+  </si>
+  <si>
+    <t>行为种类、场所、设计施行方法、着手预定日、完了预定日</t>
+  </si>
+  <si>
+    <t>一定地区计划区域的行为届出事项有哪些？</t>
+  </si>
+  <si>
+    <t>土地所有者等（包括借地权人，NPO什么的也行）需要2/3以上同意才行</t>
+  </si>
+  <si>
+    <t>都市计划区域或者准都市计划区域，认为不适合的，谁可以提案？</t>
+  </si>
+  <si>
+    <t>水泥厂、沥青厂等</t>
+  </si>
+  <si>
+    <t>开发许可的第一种特定工作物有：</t>
+  </si>
+  <si>
+    <t>高尔夫球场（任意面积）、1ha以上运动场、1ha以上墓地</t>
+  </si>
+  <si>
+    <t>开发许可的第二种特定工作物有：</t>
+  </si>
+  <si>
+    <t>不满1000平方米</t>
+  </si>
+  <si>
+    <t>不需要开发许可的，【市街化区域】面积要求：</t>
+  </si>
+  <si>
+    <t>0，必须有开发许可</t>
+  </si>
+  <si>
+    <t>不需要开发许可的，【市街化调整区域】面积要求：</t>
+  </si>
+  <si>
+    <t>不满3000平方米</t>
+  </si>
+  <si>
+    <t>不需要开发许可的，【非线引】面积要求：</t>
+  </si>
+  <si>
+    <t>不需要开发许可的，【准都市】面积要求：</t>
+  </si>
+  <si>
+    <t>不满10000平方米</t>
+  </si>
+  <si>
+    <t>不需要开发许可的，【其他】面积要求：</t>
+  </si>
+  <si>
+    <t>市街化区域以外</t>
+  </si>
+  <si>
+    <t>【农林渔业】建筑物或者自己家什么情况不需要许可：</t>
+  </si>
+  <si>
+    <t>不需要开发许可</t>
+  </si>
+  <si>
+    <t>公益、各种事业、灾害、管理或轻易行为；</t>
+  </si>
+  <si>
+    <t>位置、区域、规模</t>
+  </si>
+  <si>
+    <t>开发许可申请书记载事项1：</t>
+  </si>
+  <si>
+    <t>预定建筑物的鞥的【用途】（构造不需要）</t>
+  </si>
+  <si>
+    <t>开发许可申请书记载事项2：</t>
+  </si>
+  <si>
+    <t>开发行为相关设计（1ha以上得是资格者）</t>
+  </si>
+  <si>
+    <t>开发许可申请书记载事项3：</t>
+  </si>
+  <si>
+    <t>工事施行者等</t>
+  </si>
+  <si>
+    <t>开发许可申请书记载事项4：</t>
+  </si>
+  <si>
+    <t>技术基准（33条）、市街化调整区域还得有立地基准（34条）</t>
+  </si>
+  <si>
+    <t>开发许可基准包括：</t>
+  </si>
+  <si>
+    <t>都道府县知事</t>
+  </si>
+  <si>
+    <t>开发许可，谁要在开发登录簿上登录？</t>
+  </si>
+  <si>
+    <t>未指定用途地域的区域</t>
+  </si>
+  <si>
+    <t>都道府县知事可以在什么的区域的开发行为设置限制？</t>
+  </si>
+  <si>
+    <t>建蔽率、建筑物高度、避免位置、其他等</t>
+  </si>
+  <si>
+    <t>都道府县知事关于开发行为可以设置哪些限制？</t>
+  </si>
+  <si>
+    <t>开发审查会</t>
+  </si>
+  <si>
+    <t>关于开发许可制度不负的话，向谁进行审查请求？</t>
+  </si>
+  <si>
+    <t>轻微变更（要届出），变更为不需要开发许可的行为（许可届出都不用）</t>
+  </si>
+  <si>
+    <t>开发行为过程中，什么行为不需要许可？</t>
+  </si>
+  <si>
+    <t>立刻向都道府县知事届出</t>
+  </si>
+  <si>
+    <t>开发行为废止要怎么做？</t>
+  </si>
+  <si>
+    <t>不需要手续，直接继承</t>
+  </si>
+  <si>
+    <t>开发行为地位继承，一般继承人的手续</t>
+  </si>
+  <si>
+    <t>都道府县知事承认后可以继承</t>
+  </si>
+  <si>
+    <t>开发行为地位继承，特定继承人的手续</t>
+  </si>
+  <si>
+    <t>开发区域内，公式完了告示前能否盖建筑物？</t>
+  </si>
+  <si>
+    <t>为了工事的临时建筑物、都道府县知事认可无障碍、不同意开发行为的土地所有者等等使用权利盖</t>
+  </si>
+  <si>
+    <t>开发区域内，公式完了告示前什么情况可以盖建筑物？</t>
+  </si>
+  <si>
+    <t>开发区域内，公式完了后，能否盖预定建筑物以外的建筑？</t>
+  </si>
+  <si>
+    <t>都道府县知事许可，开发区域内的土地没定用途地域（但有建筑基准法规制）</t>
+  </si>
+  <si>
+    <t>开发区域内，公式完了后，除预定建筑物外，能盖什么建筑</t>
+  </si>
+  <si>
+    <t>原则上没有许可不能进行建筑物的新·改·用途变更和第一种工作物的新设</t>
+  </si>
+  <si>
+    <t>市街化调整区域的非开发区域，是否需要许可？</t>
+  </si>
+  <si>
+    <t>农林牧渔和公益</t>
+  </si>
+  <si>
+    <t>市街化调整区域的非开发区域，哪些不要许可？</t>
+  </si>
+  <si>
+    <t>土地形质变更、建筑物工作物的建筑、土石堆积</t>
+  </si>
+  <si>
+    <t>田园地域农地开发，什么行为必须许可？</t>
+  </si>
+  <si>
+    <t>田园地域农地开发，向谁许可？</t>
+  </si>
+  <si>
+    <t>50万</t>
+  </si>
+  <si>
+    <t>田园地域农地开发，违反罚多少钱？</t>
+  </si>
+  <si>
+    <t>通常管理轻易行为、灾害、事业、国家</t>
+  </si>
+  <si>
+    <t>田园地域农地开发，什么情况不需要许可？</t>
+  </si>
+  <si>
+    <t>规模不满300平方米</t>
+  </si>
+  <si>
+    <t>田园地域农地开发，什么情况下必须给许可？</t>
+  </si>
+  <si>
+    <t>都市计划设施、市街地开发事业（市街化和非线引）</t>
+  </si>
+  <si>
+    <t>都市计划事业都有什么？</t>
+  </si>
+  <si>
+    <t>建筑物建设、土地形质变更、工作物建设</t>
+  </si>
+  <si>
+    <t>都市计划事业认可·承认告示前，什么行为需要许可？</t>
+  </si>
+  <si>
+    <t>轻易行为、债还、事业施行行为</t>
+  </si>
+  <si>
+    <t>都市计划事业认可·承认告示前，什么行为不需要许可？</t>
+  </si>
+  <si>
+    <t>都市计划事业认可·承认告示前，需要谁许可？</t>
+  </si>
+  <si>
+    <t>建筑物建设、土地形质变更、工作物建设、5吨以上物件设置和堆积</t>
+  </si>
+  <si>
+    <t>都市计划事业认可·承认告示后，什么行为需要许可？</t>
+  </si>
+  <si>
+    <t>没有例外，都得许可</t>
+  </si>
+  <si>
+    <t>都市计划事业认可·承认告示后，需要谁许可？</t>
+  </si>
+  <si>
+    <t>事前将让渡价格等事项向施行者书面届出，施行者也可以自己把土地建物买下来</t>
+  </si>
+  <si>
+    <t>事业内土地建物等有偿让渡者要做什么？</t>
+  </si>
+  <si>
+    <t>都市计划和准都市计划区域</t>
+  </si>
+  <si>
+    <t>建筑基准法集团推定在什么区域生效？</t>
+  </si>
+  <si>
+    <t>不适用</t>
+  </si>
+  <si>
+    <t>建筑基准法国宝和文化财是否适用？</t>
+  </si>
+  <si>
+    <t>4层以上（除地面层）、高度超16米、仓库车库高度超13米</t>
+  </si>
+  <si>
+    <t>建筑基准法单体规定，大规模建筑物对象，火灾倒坏延烧防止的基准？</t>
+  </si>
+  <si>
+    <t>延展面积超3000平方米</t>
+  </si>
+  <si>
+    <t>建筑基准法单体规定，大规模建筑物对象，壁柱床什么的基准？</t>
+  </si>
+  <si>
+    <t>1000平方米</t>
+  </si>
+  <si>
+    <t>大规模木造建筑物外壁延展面积超过</t>
+  </si>
+  <si>
+    <t>防火构造</t>
+  </si>
+  <si>
+    <t>大规模木造建筑物外壁，轩里要用什么构造</t>
+  </si>
+  <si>
+    <t>防火壁·防火床要延展面积多少以上的建筑物</t>
+  </si>
+  <si>
+    <t>20米</t>
+  </si>
+  <si>
+    <t>多少米以上建筑物得弄避雷</t>
+  </si>
+  <si>
+    <t>31米</t>
+  </si>
+  <si>
+    <t>多少米以上建筑物得弄非常用升降梯</t>
+  </si>
+  <si>
+    <t>1/7以上</t>
+  </si>
+  <si>
+    <t>住宅，采光面积得是床面积的多少以上</t>
+  </si>
+  <si>
+    <t>1/5~1/10</t>
+  </si>
+  <si>
+    <t>非住宅，采光面积得是床面积的多少以上</t>
+  </si>
+  <si>
+    <t>在1/10的范围内</t>
+  </si>
+  <si>
+    <t>非住宅，采光有特殊设置的话，可以调整吗？</t>
+  </si>
+  <si>
+    <t>1/20以上</t>
+  </si>
+  <si>
+    <t>居室换气面积的窗或者开口部的面积？</t>
+  </si>
+  <si>
+    <t>4米</t>
+  </si>
+  <si>
+    <t>多少米以上算道路</t>
+  </si>
+  <si>
+    <t>特定行政厅指定的不满4米的，已存在且两边排列建筑物的</t>
+  </si>
+  <si>
+    <t>2项道路是什么？</t>
+  </si>
+  <si>
+    <t>2米</t>
+  </si>
+  <si>
+    <t>建筑物接道长度多少米以上？</t>
+  </si>
+  <si>
+    <t>周围有空地，特定行政厅经过建筑审查会同意后许可</t>
+  </si>
+  <si>
+    <t>接道不用2米的情况是？</t>
+  </si>
+  <si>
+    <t>地方共同团体，特殊建筑物或3层以上建筑物、延展超过1000平、只通过袋状道路连接的延展面积超过150的建筑（一户建除外）</t>
+  </si>
+  <si>
+    <t>什么情况下对接道义务限制可以附加【不能缓和】</t>
+  </si>
+  <si>
+    <t>所得税、登录免许税、印纸税</t>
+  </si>
+  <si>
+    <t>属于国税的有哪些？</t>
+  </si>
+  <si>
+    <t>（3种）</t>
+  </si>
+  <si>
+    <t>税</t>
+  </si>
+  <si>
+    <t>不动产取得税、固定资产税</t>
+  </si>
+  <si>
+    <t>属于地方税的有哪些？</t>
+  </si>
+  <si>
+    <t>（2种）</t>
   </si>
 </sst>
 </file>
@@ -684,8 +3093,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1221,8 +3639,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E417"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="68.8333333333333" customWidth="1"/>
+    <col min="3" max="3" width="57.4166666666667" customWidth="1"/>
+    <col min="4" max="5" width="29.0833333333333" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1245,13 +3668,10 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
@@ -1262,14 +3682,11 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>5</v>
+      <c r="B3" t="s">
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1279,34 +3696,5904 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>18</v>
+      <c r="B4" t="s">
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" t="s">
+        <v>101</v>
+      </c>
+      <c r="E50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" t="s">
+        <v>105</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" t="s">
+        <v>109</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s">
+        <v>117</v>
+      </c>
+      <c r="E58" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" t="s">
+        <v>119</v>
+      </c>
+      <c r="E59" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" t="s">
+        <v>123</v>
+      </c>
+      <c r="E61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" t="s">
+        <v>125</v>
+      </c>
+      <c r="E62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>1000</v>
+      </c>
+      <c r="C63" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>500</v>
+      </c>
+      <c r="C64" t="s">
+        <v>128</v>
+      </c>
+      <c r="D64" t="s">
+        <v>127</v>
+      </c>
+      <c r="E64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>100</v>
+      </c>
+      <c r="C65" t="s">
+        <v>129</v>
+      </c>
+      <c r="D65" t="s">
+        <v>130</v>
+      </c>
+      <c r="E65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>90</v>
+      </c>
+      <c r="C66" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" t="s">
+        <v>130</v>
+      </c>
+      <c r="E66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>80</v>
+      </c>
+      <c r="C67" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" t="s">
+        <v>130</v>
+      </c>
+      <c r="E67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" t="s">
+        <v>134</v>
+      </c>
+      <c r="D68" t="s">
+        <v>135</v>
+      </c>
+      <c r="E68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" t="s">
+        <v>138</v>
+      </c>
+      <c r="E69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" t="s">
+        <v>140</v>
+      </c>
+      <c r="D70" t="s">
+        <v>141</v>
+      </c>
+      <c r="E70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" t="s">
+        <v>143</v>
+      </c>
+      <c r="E71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" t="s">
+        <v>145</v>
+      </c>
+      <c r="E72" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" t="s">
+        <v>147</v>
+      </c>
+      <c r="E73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" t="s">
+        <v>149</v>
+      </c>
+      <c r="D74" t="s">
+        <v>150</v>
+      </c>
+      <c r="E74" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" t="s">
+        <v>152</v>
+      </c>
+      <c r="E75" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" t="s">
+        <v>154</v>
+      </c>
+      <c r="E76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>90</v>
+      </c>
+      <c r="C77" t="s">
+        <v>155</v>
+      </c>
+      <c r="D77" t="s">
+        <v>127</v>
+      </c>
+      <c r="E77" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>60</v>
+      </c>
+      <c r="C78" t="s">
+        <v>156</v>
+      </c>
+      <c r="D78" t="s">
+        <v>127</v>
+      </c>
+      <c r="E78" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" t="s">
+        <v>158</v>
+      </c>
+      <c r="E79" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" t="s">
+        <v>160</v>
+      </c>
+      <c r="E80" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" t="s">
+        <v>162</v>
+      </c>
+      <c r="D81" t="s">
+        <v>163</v>
+      </c>
+      <c r="E81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" t="s">
+        <v>165</v>
+      </c>
+      <c r="D82" t="s">
+        <v>166</v>
+      </c>
+      <c r="E82" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" t="s">
+        <v>168</v>
+      </c>
+      <c r="D83" t="s">
+        <v>169</v>
+      </c>
+      <c r="E83" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" t="s">
+        <v>171</v>
+      </c>
+      <c r="D84" t="s">
+        <v>172</v>
+      </c>
+      <c r="E84" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>173</v>
+      </c>
+      <c r="C85" t="s">
+        <v>174</v>
+      </c>
+      <c r="D85" t="s">
+        <v>175</v>
+      </c>
+      <c r="E85" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" t="s">
+        <v>177</v>
+      </c>
+      <c r="D86" t="s">
+        <v>138</v>
+      </c>
+      <c r="E86" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" t="s">
+        <v>179</v>
+      </c>
+      <c r="D87" t="s">
+        <v>138</v>
+      </c>
+      <c r="E87" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" t="s">
+        <v>181</v>
+      </c>
+      <c r="D88" t="s">
+        <v>182</v>
+      </c>
+      <c r="E88" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>183</v>
+      </c>
+      <c r="C89" t="s">
+        <v>184</v>
+      </c>
+      <c r="E89" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>185</v>
+      </c>
+      <c r="C90" t="s">
+        <v>186</v>
+      </c>
+      <c r="E90" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>187</v>
+      </c>
+      <c r="C91" t="s">
+        <v>188</v>
+      </c>
+      <c r="D91" t="s">
+        <v>189</v>
+      </c>
+      <c r="E91" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" t="s">
+        <v>191</v>
+      </c>
+      <c r="D92" t="s">
+        <v>141</v>
+      </c>
+      <c r="E92" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>192</v>
+      </c>
+      <c r="C93" t="s">
+        <v>193</v>
+      </c>
+      <c r="E93" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>194</v>
+      </c>
+      <c r="C94" t="s">
+        <v>195</v>
+      </c>
+      <c r="D94" t="s">
+        <v>138</v>
+      </c>
+      <c r="E94" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>196</v>
+      </c>
+      <c r="C95" t="s">
+        <v>197</v>
+      </c>
+      <c r="D95" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>199</v>
+      </c>
+      <c r="C96" t="s">
+        <v>200</v>
+      </c>
+      <c r="E96" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>201</v>
+      </c>
+      <c r="E97" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>28</v>
+      </c>
+      <c r="C98" t="s">
+        <v>202</v>
+      </c>
+      <c r="E98" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" t="s">
+        <v>203</v>
+      </c>
+      <c r="E99" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" t="s">
+        <v>205</v>
+      </c>
+      <c r="E100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>206</v>
+      </c>
+      <c r="C101" t="s">
+        <v>207</v>
+      </c>
+      <c r="E101" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" t="s">
+        <v>208</v>
+      </c>
+      <c r="E102" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>209</v>
+      </c>
+      <c r="C103" t="s">
+        <v>210</v>
+      </c>
+      <c r="E103" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>211</v>
+      </c>
+      <c r="C104" t="s">
+        <v>212</v>
+      </c>
+      <c r="E104" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>213</v>
+      </c>
+      <c r="C105" t="s">
+        <v>214</v>
+      </c>
+      <c r="E105" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>215</v>
+      </c>
+      <c r="C106" t="s">
+        <v>216</v>
+      </c>
+      <c r="E106" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>217</v>
+      </c>
+      <c r="C107" t="s">
+        <v>218</v>
+      </c>
+      <c r="E107" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" t="s">
+        <v>220</v>
+      </c>
+      <c r="E108" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>217</v>
+      </c>
+      <c r="C109" t="s">
+        <v>221</v>
+      </c>
+      <c r="E109" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>222</v>
+      </c>
+      <c r="C110" t="s">
+        <v>223</v>
+      </c>
+      <c r="E110" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>224</v>
+      </c>
+      <c r="C111" t="s">
+        <v>225</v>
+      </c>
+      <c r="E111" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>226</v>
+      </c>
+      <c r="C112" t="s">
+        <v>227</v>
+      </c>
+      <c r="E112" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>228</v>
+      </c>
+      <c r="C113" t="s">
+        <v>229</v>
+      </c>
+      <c r="E113" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>230</v>
+      </c>
+      <c r="C114" t="s">
+        <v>231</v>
+      </c>
+      <c r="E114" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>217</v>
+      </c>
+      <c r="C115" t="s">
+        <v>232</v>
+      </c>
+      <c r="E115" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>233</v>
+      </c>
+      <c r="C116" t="s">
+        <v>234</v>
+      </c>
+      <c r="E116" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>235</v>
+      </c>
+      <c r="C117" t="s">
+        <v>236</v>
+      </c>
+      <c r="E117" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>237</v>
+      </c>
+      <c r="C118" t="s">
+        <v>238</v>
+      </c>
+      <c r="E118" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>239</v>
+      </c>
+      <c r="C119" t="s">
+        <v>240</v>
+      </c>
+      <c r="E119" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>241</v>
+      </c>
+      <c r="C120" t="s">
+        <v>242</v>
+      </c>
+      <c r="E120" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>243</v>
+      </c>
+      <c r="C121" t="s">
+        <v>244</v>
+      </c>
+      <c r="E121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>245</v>
+      </c>
+      <c r="C122" t="s">
+        <v>246</v>
+      </c>
+      <c r="E122" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>247</v>
+      </c>
+      <c r="C123" t="s">
+        <v>248</v>
+      </c>
+      <c r="E123" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>249</v>
+      </c>
+      <c r="C124" t="s">
+        <v>250</v>
+      </c>
+      <c r="E124" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>251</v>
+      </c>
+      <c r="C125" t="s">
+        <v>252</v>
+      </c>
+      <c r="E125" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>253</v>
+      </c>
+      <c r="C126" t="s">
+        <v>254</v>
+      </c>
+      <c r="E126" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>255</v>
+      </c>
+      <c r="C127" t="s">
+        <v>256</v>
+      </c>
+      <c r="E127" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>257</v>
+      </c>
+      <c r="C128" t="s">
+        <v>258</v>
+      </c>
+      <c r="E128" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>259</v>
+      </c>
+      <c r="C129" t="s">
+        <v>260</v>
+      </c>
+      <c r="E129" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>261</v>
+      </c>
+      <c r="C130" t="s">
+        <v>262</v>
+      </c>
+      <c r="E130" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>263</v>
+      </c>
+      <c r="C131" t="s">
+        <v>264</v>
+      </c>
+      <c r="E131" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132" t="s">
+        <v>266</v>
+      </c>
+      <c r="E132" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>267</v>
+      </c>
+      <c r="C133" t="s">
+        <v>268</v>
+      </c>
+      <c r="E133" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>269</v>
+      </c>
+      <c r="C134" t="s">
+        <v>270</v>
+      </c>
+      <c r="E134" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>271</v>
+      </c>
+      <c r="C135" t="s">
+        <v>272</v>
+      </c>
+      <c r="E135" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>273</v>
+      </c>
+      <c r="C136" t="s">
+        <v>274</v>
+      </c>
+      <c r="E136" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>275</v>
+      </c>
+      <c r="C137" t="s">
+        <v>276</v>
+      </c>
+      <c r="E137" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>277</v>
+      </c>
+      <c r="C138" t="s">
+        <v>278</v>
+      </c>
+      <c r="E138" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>279</v>
+      </c>
+      <c r="C139" t="s">
+        <v>280</v>
+      </c>
+      <c r="E139" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>281</v>
+      </c>
+      <c r="C140" t="s">
+        <v>282</v>
+      </c>
+      <c r="E140" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>283</v>
+      </c>
+      <c r="C141" t="s">
+        <v>284</v>
+      </c>
+      <c r="E141" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>285</v>
+      </c>
+      <c r="C142" t="s">
+        <v>286</v>
+      </c>
+      <c r="E142" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>287</v>
+      </c>
+      <c r="C143" t="s">
+        <v>288</v>
+      </c>
+      <c r="D143" t="s">
+        <v>289</v>
+      </c>
+      <c r="E143" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>290</v>
+      </c>
+      <c r="C144" t="s">
+        <v>291</v>
+      </c>
+      <c r="D144" t="s">
+        <v>292</v>
+      </c>
+      <c r="E144" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>293</v>
+      </c>
+      <c r="C145" t="s">
+        <v>294</v>
+      </c>
+      <c r="E145" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>295</v>
+      </c>
+      <c r="C146" t="s">
+        <v>296</v>
+      </c>
+      <c r="E146" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>297</v>
+      </c>
+      <c r="C147" t="s">
+        <v>298</v>
+      </c>
+      <c r="E147" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>299</v>
+      </c>
+      <c r="C148" t="s">
+        <v>300</v>
+      </c>
+      <c r="E148" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>301</v>
+      </c>
+      <c r="C149" t="s">
+        <v>302</v>
+      </c>
+      <c r="E149" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>303</v>
+      </c>
+      <c r="C150" t="s">
+        <v>304</v>
+      </c>
+      <c r="E150" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>305</v>
+      </c>
+      <c r="C151" t="s">
+        <v>306</v>
+      </c>
+      <c r="E151" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>307</v>
+      </c>
+      <c r="C152" t="s">
+        <v>308</v>
+      </c>
+      <c r="E152" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>309</v>
+      </c>
+      <c r="C153" t="s">
+        <v>310</v>
+      </c>
+      <c r="E153" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>311</v>
+      </c>
+      <c r="C154" t="s">
+        <v>312</v>
+      </c>
+      <c r="E154" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>313</v>
+      </c>
+      <c r="C155" t="s">
+        <v>314</v>
+      </c>
+      <c r="E155" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>315</v>
+      </c>
+      <c r="C156" t="s">
+        <v>316</v>
+      </c>
+      <c r="E156" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>317</v>
+      </c>
+      <c r="C157" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>319</v>
+      </c>
+      <c r="C158" t="s">
+        <v>320</v>
+      </c>
+      <c r="E158" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>321</v>
+      </c>
+      <c r="C159" t="s">
+        <v>322</v>
+      </c>
+      <c r="E159" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>323</v>
+      </c>
+      <c r="C160" t="s">
+        <v>324</v>
+      </c>
+      <c r="E160" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>325</v>
+      </c>
+      <c r="C161" t="s">
+        <v>326</v>
+      </c>
+      <c r="E161" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>327</v>
+      </c>
+      <c r="C162" t="s">
+        <v>328</v>
+      </c>
+      <c r="E162" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>329</v>
+      </c>
+      <c r="C163" t="s">
+        <v>330</v>
+      </c>
+      <c r="E163" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>331</v>
+      </c>
+      <c r="C164" t="s">
+        <v>332</v>
+      </c>
+      <c r="E164" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>333</v>
+      </c>
+      <c r="C165" t="s">
+        <v>334</v>
+      </c>
+      <c r="E165" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>335</v>
+      </c>
+      <c r="C166" t="s">
+        <v>336</v>
+      </c>
+      <c r="E166" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>337</v>
+      </c>
+      <c r="C167" t="s">
+        <v>338</v>
+      </c>
+      <c r="E167" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>339</v>
+      </c>
+      <c r="C168" t="s">
+        <v>340</v>
+      </c>
+      <c r="E168" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>341</v>
+      </c>
+      <c r="C169" t="s">
+        <v>342</v>
+      </c>
+      <c r="E169" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>343</v>
+      </c>
+      <c r="C170" t="s">
+        <v>344</v>
+      </c>
+      <c r="E170" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>345</v>
+      </c>
+      <c r="C171" t="s">
+        <v>346</v>
+      </c>
+      <c r="E171" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>347</v>
+      </c>
+      <c r="C172" t="s">
+        <v>348</v>
+      </c>
+      <c r="E172" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>349</v>
+      </c>
+      <c r="C173" t="s">
+        <v>350</v>
+      </c>
+      <c r="E173" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>351</v>
+      </c>
+      <c r="C174" t="s">
+        <v>352</v>
+      </c>
+      <c r="E174" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>353</v>
+      </c>
+      <c r="C175" t="s">
+        <v>354</v>
+      </c>
+      <c r="E175" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>355</v>
+      </c>
+      <c r="C176" t="s">
+        <v>356</v>
+      </c>
+      <c r="E176" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>357</v>
+      </c>
+      <c r="C177" t="s">
+        <v>358</v>
+      </c>
+      <c r="E177" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>359</v>
+      </c>
+      <c r="C178" t="s">
+        <v>360</v>
+      </c>
+      <c r="E178" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>361</v>
+      </c>
+      <c r="C179" t="s">
+        <v>362</v>
+      </c>
+      <c r="E179" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>363</v>
+      </c>
+      <c r="C180" t="s">
+        <v>364</v>
+      </c>
+      <c r="E180" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>365</v>
+      </c>
+      <c r="C181" t="s">
+        <v>366</v>
+      </c>
+      <c r="E181" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>367</v>
+      </c>
+      <c r="C182" t="s">
+        <v>368</v>
+      </c>
+      <c r="E182" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>369</v>
+      </c>
+      <c r="C183" t="s">
+        <v>370</v>
+      </c>
+      <c r="E183" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>371</v>
+      </c>
+      <c r="C184" t="s">
+        <v>372</v>
+      </c>
+      <c r="E184" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>373</v>
+      </c>
+      <c r="C185" t="s">
+        <v>374</v>
+      </c>
+      <c r="E185" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>375</v>
+      </c>
+      <c r="C186" t="s">
+        <v>376</v>
+      </c>
+      <c r="E186" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>377</v>
+      </c>
+      <c r="C187" t="s">
+        <v>378</v>
+      </c>
+      <c r="E187" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>379</v>
+      </c>
+      <c r="C188" t="s">
+        <v>380</v>
+      </c>
+      <c r="E188" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>381</v>
+      </c>
+      <c r="C189" t="s">
+        <v>382</v>
+      </c>
+      <c r="E189" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>383</v>
+      </c>
+      <c r="C190" t="s">
+        <v>384</v>
+      </c>
+      <c r="E190" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>385</v>
+      </c>
+      <c r="C191" t="s">
+        <v>386</v>
+      </c>
+      <c r="E191" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>387</v>
+      </c>
+      <c r="C192" t="s">
+        <v>388</v>
+      </c>
+      <c r="E192" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>389</v>
+      </c>
+      <c r="C193" t="s">
+        <v>390</v>
+      </c>
+      <c r="E193" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>391</v>
+      </c>
+      <c r="C194" t="s">
+        <v>392</v>
+      </c>
+      <c r="E194" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>393</v>
+      </c>
+      <c r="C195" t="s">
+        <v>394</v>
+      </c>
+      <c r="E195" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>395</v>
+      </c>
+      <c r="C196" t="s">
+        <v>396</v>
+      </c>
+      <c r="E196" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>397</v>
+      </c>
+      <c r="C197" t="s">
+        <v>398</v>
+      </c>
+      <c r="E197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>399</v>
+      </c>
+      <c r="C198" t="s">
+        <v>400</v>
+      </c>
+      <c r="E198" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>401</v>
+      </c>
+      <c r="C199" t="s">
+        <v>402</v>
+      </c>
+      <c r="E199" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>403</v>
+      </c>
+      <c r="C200" t="s">
+        <v>404</v>
+      </c>
+      <c r="E200" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>405</v>
+      </c>
+      <c r="C201" t="s">
+        <v>406</v>
+      </c>
+      <c r="E201" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>407</v>
+      </c>
+      <c r="C202" t="s">
+        <v>408</v>
+      </c>
+      <c r="E202" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>409</v>
+      </c>
+      <c r="C203" t="s">
+        <v>410</v>
+      </c>
+      <c r="E203" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>411</v>
+      </c>
+      <c r="C204" t="s">
+        <v>412</v>
+      </c>
+      <c r="E204" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>413</v>
+      </c>
+      <c r="C205" t="s">
+        <v>414</v>
+      </c>
+      <c r="D205" t="s">
+        <v>415</v>
+      </c>
+      <c r="E205" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C206" t="s">
+        <v>417</v>
+      </c>
+      <c r="D206" t="s">
+        <v>418</v>
+      </c>
+      <c r="E206" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>419</v>
+      </c>
+      <c r="C207" t="s">
+        <v>420</v>
+      </c>
+      <c r="E207" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C208" t="s">
+        <v>421</v>
+      </c>
+      <c r="D208" t="s">
+        <v>418</v>
+      </c>
+      <c r="E208" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>422</v>
+      </c>
+      <c r="C209" t="s">
+        <v>423</v>
+      </c>
+      <c r="E209" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>424</v>
+      </c>
+      <c r="C210" t="s">
+        <v>425</v>
+      </c>
+      <c r="E210" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>422</v>
+      </c>
+      <c r="C211" t="s">
+        <v>426</v>
+      </c>
+      <c r="E211" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>424</v>
+      </c>
+      <c r="C212" t="s">
+        <v>427</v>
+      </c>
+      <c r="E212" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>428</v>
+      </c>
+      <c r="C213" t="s">
+        <v>429</v>
+      </c>
+      <c r="E213" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>430</v>
+      </c>
+      <c r="C214" t="s">
+        <v>431</v>
+      </c>
+      <c r="E214" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>432</v>
+      </c>
+      <c r="C215" t="s">
+        <v>433</v>
+      </c>
+      <c r="E215" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>434</v>
+      </c>
+      <c r="C216" t="s">
+        <v>435</v>
+      </c>
+      <c r="E216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>436</v>
+      </c>
+      <c r="C217" t="s">
+        <v>437</v>
+      </c>
+      <c r="E217" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>30</v>
+      </c>
+      <c r="C218" t="s">
+        <v>438</v>
+      </c>
+      <c r="E218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C219" t="s">
+        <v>440</v>
+      </c>
+      <c r="E219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>441</v>
+      </c>
+      <c r="C220" t="s">
+        <v>442</v>
+      </c>
+      <c r="E220" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>443</v>
+      </c>
+      <c r="C221" t="s">
+        <v>444</v>
+      </c>
+      <c r="E221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>445</v>
+      </c>
+      <c r="C222" t="s">
+        <v>446</v>
+      </c>
+      <c r="E222" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C223" t="s">
+        <v>447</v>
+      </c>
+      <c r="E223" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>448</v>
+      </c>
+      <c r="C224" t="s">
+        <v>449</v>
+      </c>
+      <c r="E224" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>450</v>
+      </c>
+      <c r="C225" t="s">
+        <v>451</v>
+      </c>
+      <c r="E225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>1</v>
+      </c>
+      <c r="C226" t="s">
+        <v>452</v>
+      </c>
+      <c r="D226" t="s">
+        <v>453</v>
+      </c>
+      <c r="E226" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>2</v>
+      </c>
+      <c r="C227" t="s">
+        <v>454</v>
+      </c>
+      <c r="D227" t="s">
+        <v>453</v>
+      </c>
+      <c r="E227" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>455</v>
+      </c>
+      <c r="C228" t="s">
+        <v>456</v>
+      </c>
+      <c r="E228" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>457</v>
+      </c>
+      <c r="C229" t="s">
+        <v>458</v>
+      </c>
+      <c r="E229" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>459</v>
+      </c>
+      <c r="C230" t="s">
+        <v>460</v>
+      </c>
+      <c r="E230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>461</v>
+      </c>
+      <c r="C231" t="s">
+        <v>462</v>
+      </c>
+      <c r="E231" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>463</v>
+      </c>
+      <c r="C232" t="s">
+        <v>464</v>
+      </c>
+      <c r="E232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>465</v>
+      </c>
+      <c r="C233" t="s">
+        <v>466</v>
+      </c>
+      <c r="E233" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>467</v>
+      </c>
+      <c r="C234" t="s">
+        <v>468</v>
+      </c>
+      <c r="E234" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>469</v>
+      </c>
+      <c r="C235" t="s">
+        <v>470</v>
+      </c>
+      <c r="E235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>471</v>
+      </c>
+      <c r="C236" t="s">
+        <v>472</v>
+      </c>
+      <c r="E236" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>473</v>
+      </c>
+      <c r="C237" t="s">
+        <v>474</v>
+      </c>
+      <c r="E237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>475</v>
+      </c>
+      <c r="C238" t="s">
+        <v>476</v>
+      </c>
+      <c r="E238" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>477</v>
+      </c>
+      <c r="C239" t="s">
+        <v>478</v>
+      </c>
+      <c r="E239" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>479</v>
+      </c>
+      <c r="C240" t="s">
+        <v>480</v>
+      </c>
+      <c r="E240" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>481</v>
+      </c>
+      <c r="C241" t="s">
+        <v>482</v>
+      </c>
+      <c r="E241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>483</v>
+      </c>
+      <c r="C242" t="s">
+        <v>484</v>
+      </c>
+      <c r="E242" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>485</v>
+      </c>
+      <c r="C243" t="s">
+        <v>486</v>
+      </c>
+      <c r="E243" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>487</v>
+      </c>
+      <c r="C244" t="s">
+        <v>488</v>
+      </c>
+      <c r="E244" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>489</v>
+      </c>
+      <c r="C245" t="s">
+        <v>490</v>
+      </c>
+      <c r="E245" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>491</v>
+      </c>
+      <c r="C246" t="s">
+        <v>492</v>
+      </c>
+      <c r="E246" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>493</v>
+      </c>
+      <c r="C247" t="s">
+        <v>494</v>
+      </c>
+      <c r="E247" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>495</v>
+      </c>
+      <c r="C248" t="s">
+        <v>496</v>
+      </c>
+      <c r="E248" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>497</v>
+      </c>
+      <c r="C249" t="s">
+        <v>498</v>
+      </c>
+      <c r="E249" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>499</v>
+      </c>
+      <c r="C250" t="s">
+        <v>500</v>
+      </c>
+      <c r="E250" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>501</v>
+      </c>
+      <c r="C251" t="s">
+        <v>502</v>
+      </c>
+      <c r="E251" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>503</v>
+      </c>
+      <c r="C252" t="s">
+        <v>504</v>
+      </c>
+      <c r="E252" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>65</v>
+      </c>
+      <c r="C253" t="s">
+        <v>505</v>
+      </c>
+      <c r="E253" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>506</v>
+      </c>
+      <c r="C254" t="s">
+        <v>507</v>
+      </c>
+      <c r="E254" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>508</v>
+      </c>
+      <c r="C255" t="s">
+        <v>509</v>
+      </c>
+      <c r="E255" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>510</v>
+      </c>
+      <c r="C256" t="s">
+        <v>511</v>
+      </c>
+      <c r="E256" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>512</v>
+      </c>
+      <c r="C257" t="s">
+        <v>513</v>
+      </c>
+      <c r="E257" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>514</v>
+      </c>
+      <c r="C258" t="s">
+        <v>515</v>
+      </c>
+      <c r="E258" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>63</v>
+      </c>
+      <c r="C259" t="s">
+        <v>516</v>
+      </c>
+      <c r="E259" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>517</v>
+      </c>
+      <c r="C260" t="s">
+        <v>518</v>
+      </c>
+      <c r="E260" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>519</v>
+      </c>
+      <c r="C261" t="s">
+        <v>520</v>
+      </c>
+      <c r="E261" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>521</v>
+      </c>
+      <c r="C262" t="s">
+        <v>522</v>
+      </c>
+      <c r="E262" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>523</v>
+      </c>
+      <c r="C263" t="s">
+        <v>524</v>
+      </c>
+      <c r="E263" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>525</v>
+      </c>
+      <c r="C264" t="s">
+        <v>526</v>
+      </c>
+      <c r="E264" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>527</v>
+      </c>
+      <c r="C265" t="s">
+        <v>528</v>
+      </c>
+      <c r="E265" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>481</v>
+      </c>
+      <c r="C266" t="s">
+        <v>529</v>
+      </c>
+      <c r="E266" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>530</v>
+      </c>
+      <c r="C267" t="s">
+        <v>531</v>
+      </c>
+      <c r="E267" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>495</v>
+      </c>
+      <c r="C268" t="s">
+        <v>532</v>
+      </c>
+      <c r="E268" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>533</v>
+      </c>
+      <c r="C269" t="s">
+        <v>534</v>
+      </c>
+      <c r="E269" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>535</v>
+      </c>
+      <c r="C270" t="s">
+        <v>536</v>
+      </c>
+      <c r="E270" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>537</v>
+      </c>
+      <c r="C271" t="s">
+        <v>538</v>
+      </c>
+      <c r="E271" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>539</v>
+      </c>
+      <c r="C272" t="s">
+        <v>540</v>
+      </c>
+      <c r="E272" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>541</v>
+      </c>
+      <c r="C273" t="s">
+        <v>542</v>
+      </c>
+      <c r="E273" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>543</v>
+      </c>
+      <c r="C274" t="s">
+        <v>544</v>
+      </c>
+      <c r="E274" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>75</v>
+      </c>
+      <c r="C275" t="s">
+        <v>545</v>
+      </c>
+      <c r="E275" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>546</v>
+      </c>
+      <c r="C276" t="s">
+        <v>547</v>
+      </c>
+      <c r="E276" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>548</v>
+      </c>
+      <c r="C277" t="s">
+        <v>549</v>
+      </c>
+      <c r="E277" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>550</v>
+      </c>
+      <c r="C278" t="s">
+        <v>551</v>
+      </c>
+      <c r="E278" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>543</v>
+      </c>
+      <c r="C279" t="s">
+        <v>552</v>
+      </c>
+      <c r="E279" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>75</v>
+      </c>
+      <c r="C280" t="s">
+        <v>553</v>
+      </c>
+      <c r="E280" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>554</v>
+      </c>
+      <c r="C281" t="s">
+        <v>555</v>
+      </c>
+      <c r="E281" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>65</v>
+      </c>
+      <c r="C282" t="s">
+        <v>556</v>
+      </c>
+      <c r="E282" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>557</v>
+      </c>
+      <c r="C283" t="s">
+        <v>558</v>
+      </c>
+      <c r="E283" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>559</v>
+      </c>
+      <c r="C284" t="s">
+        <v>560</v>
+      </c>
+      <c r="E284" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>508</v>
+      </c>
+      <c r="C285" t="s">
+        <v>561</v>
+      </c>
+      <c r="E285" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>562</v>
+      </c>
+      <c r="C286" t="s">
+        <v>563</v>
+      </c>
+      <c r="E286" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>564</v>
+      </c>
+      <c r="C287" t="s">
+        <v>565</v>
+      </c>
+      <c r="E287" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>566</v>
+      </c>
+      <c r="C288" t="s">
+        <v>567</v>
+      </c>
+      <c r="E288" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>481</v>
+      </c>
+      <c r="C289" t="s">
+        <v>568</v>
+      </c>
+      <c r="E289" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>569</v>
+      </c>
+      <c r="C290" t="s">
+        <v>570</v>
+      </c>
+      <c r="E290" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>571</v>
+      </c>
+      <c r="C291" t="s">
+        <v>572</v>
+      </c>
+      <c r="E291" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>573</v>
+      </c>
+      <c r="C292" t="s">
+        <v>574</v>
+      </c>
+      <c r="E292" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>575</v>
+      </c>
+      <c r="C293" t="s">
+        <v>576</v>
+      </c>
+      <c r="E293" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>497</v>
+      </c>
+      <c r="C294" t="s">
+        <v>577</v>
+      </c>
+      <c r="E294" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
+        <v>578</v>
+      </c>
+      <c r="C295" t="s">
+        <v>579</v>
+      </c>
+      <c r="E295" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
+        <v>580</v>
+      </c>
+      <c r="C296" t="s">
+        <v>581</v>
+      </c>
+      <c r="E296" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
+        <v>489</v>
+      </c>
+      <c r="C297" t="s">
+        <v>582</v>
+      </c>
+      <c r="E297" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
+        <v>583</v>
+      </c>
+      <c r="C298" t="s">
+        <v>584</v>
+      </c>
+      <c r="E298" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
+        <v>585</v>
+      </c>
+      <c r="C299" t="s">
+        <v>586</v>
+      </c>
+      <c r="E299" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
+        <v>587</v>
+      </c>
+      <c r="C300" t="s">
+        <v>588</v>
+      </c>
+      <c r="E300" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
+        <v>495</v>
+      </c>
+      <c r="C301" t="s">
+        <v>589</v>
+      </c>
+      <c r="E301" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302" t="s">
+        <v>590</v>
+      </c>
+      <c r="C302" t="s">
+        <v>591</v>
+      </c>
+      <c r="E302" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303" t="s">
+        <v>592</v>
+      </c>
+      <c r="C303" t="s">
+        <v>593</v>
+      </c>
+      <c r="E303" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304" t="s">
+        <v>594</v>
+      </c>
+      <c r="C304" t="s">
+        <v>595</v>
+      </c>
+      <c r="E304" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
+        <v>596</v>
+      </c>
+      <c r="C305" t="s">
+        <v>597</v>
+      </c>
+      <c r="E305" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306" t="s">
+        <v>598</v>
+      </c>
+      <c r="C306" t="s">
+        <v>599</v>
+      </c>
+      <c r="E306" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307" t="s">
+        <v>600</v>
+      </c>
+      <c r="C307" t="s">
+        <v>601</v>
+      </c>
+      <c r="E307" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308" t="s">
+        <v>602</v>
+      </c>
+      <c r="C308" t="s">
+        <v>603</v>
+      </c>
+      <c r="E308" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309" t="s">
+        <v>604</v>
+      </c>
+      <c r="C309" t="s">
+        <v>605</v>
+      </c>
+      <c r="D309" t="s">
+        <v>606</v>
+      </c>
+      <c r="E309" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>10</v>
+      </c>
+      <c r="C310" t="s">
+        <v>607</v>
+      </c>
+      <c r="E310" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>55</v>
+      </c>
+      <c r="C311" t="s">
+        <v>608</v>
+      </c>
+      <c r="E311" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" t="s">
+        <v>609</v>
+      </c>
+      <c r="C312" t="s">
+        <v>610</v>
+      </c>
+      <c r="E312" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" t="s">
+        <v>611</v>
+      </c>
+      <c r="C313" t="s">
+        <v>612</v>
+      </c>
+      <c r="E313" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314">
+        <v>1001</v>
+      </c>
+      <c r="B314" t="s">
+        <v>613</v>
+      </c>
+      <c r="C314" t="s">
+        <v>614</v>
+      </c>
+      <c r="D314" t="s">
+        <v>615</v>
+      </c>
+      <c r="E314" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315">
+        <v>1002</v>
+      </c>
+      <c r="B315" t="s">
+        <v>617</v>
+      </c>
+      <c r="C315" t="s">
+        <v>618</v>
+      </c>
+      <c r="E315" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316">
+        <v>1003</v>
+      </c>
+      <c r="B316" t="s">
+        <v>617</v>
+      </c>
+      <c r="C316" t="s">
+        <v>619</v>
+      </c>
+      <c r="E316" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317">
+        <v>1004</v>
+      </c>
+      <c r="B317" t="s">
+        <v>620</v>
+      </c>
+      <c r="C317" t="s">
+        <v>621</v>
+      </c>
+      <c r="E317" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318">
+        <v>2001</v>
+      </c>
+      <c r="B318" t="s">
+        <v>622</v>
+      </c>
+      <c r="C318" t="s">
+        <v>623</v>
+      </c>
+      <c r="E318" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319">
+        <v>2002</v>
+      </c>
+      <c r="B319" t="s">
+        <v>625</v>
+      </c>
+      <c r="C319" t="s">
+        <v>626</v>
+      </c>
+      <c r="E319" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320">
+        <v>2003</v>
+      </c>
+      <c r="B320" t="s">
+        <v>627</v>
+      </c>
+      <c r="C320" t="s">
+        <v>628</v>
+      </c>
+      <c r="E320" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321">
+        <v>2004</v>
+      </c>
+      <c r="B321" t="s">
+        <v>629</v>
+      </c>
+      <c r="C321" t="s">
+        <v>630</v>
+      </c>
+      <c r="E321" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322">
+        <v>2005</v>
+      </c>
+      <c r="B322" t="s">
+        <v>631</v>
+      </c>
+      <c r="C322" t="s">
+        <v>632</v>
+      </c>
+      <c r="E322" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323">
+        <v>2006</v>
+      </c>
+      <c r="B323" t="s">
+        <v>633</v>
+      </c>
+      <c r="C323" t="s">
+        <v>634</v>
+      </c>
+      <c r="E323" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324">
+        <v>2007</v>
+      </c>
+      <c r="B324" t="s">
+        <v>635</v>
+      </c>
+      <c r="C324" t="s">
+        <v>636</v>
+      </c>
+      <c r="E324" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325">
+        <v>2008</v>
+      </c>
+      <c r="B325" t="s">
+        <v>637</v>
+      </c>
+      <c r="C325" t="s">
+        <v>638</v>
+      </c>
+      <c r="E325" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326">
+        <v>2009</v>
+      </c>
+      <c r="B326" t="s">
+        <v>639</v>
+      </c>
+      <c r="C326" t="s">
+        <v>640</v>
+      </c>
+      <c r="E326" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327">
+        <v>2010</v>
+      </c>
+      <c r="B327" t="s">
+        <v>641</v>
+      </c>
+      <c r="C327" t="s">
+        <v>642</v>
+      </c>
+      <c r="E327" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328">
+        <v>2011</v>
+      </c>
+      <c r="B328" t="s">
+        <v>643</v>
+      </c>
+      <c r="C328" t="s">
+        <v>644</v>
+      </c>
+      <c r="E328" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329">
+        <v>2012</v>
+      </c>
+      <c r="B329" t="s">
+        <v>645</v>
+      </c>
+      <c r="C329" t="s">
+        <v>646</v>
+      </c>
+      <c r="E329" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330">
+        <v>2013</v>
+      </c>
+      <c r="B330" t="s">
+        <v>647</v>
+      </c>
+      <c r="C330" t="s">
+        <v>648</v>
+      </c>
+      <c r="E330" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331">
+        <v>2014</v>
+      </c>
+      <c r="B331" t="s">
+        <v>649</v>
+      </c>
+      <c r="C331" t="s">
+        <v>650</v>
+      </c>
+      <c r="E331" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332">
+        <v>2015</v>
+      </c>
+      <c r="B332" t="s">
+        <v>651</v>
+      </c>
+      <c r="C332" t="s">
+        <v>652</v>
+      </c>
+      <c r="E332" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333">
+        <v>2016</v>
+      </c>
+      <c r="B333" t="s">
+        <v>653</v>
+      </c>
+      <c r="C333" t="s">
+        <v>654</v>
+      </c>
+      <c r="E333" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334">
+        <v>2017</v>
+      </c>
+      <c r="B334" t="s">
+        <v>655</v>
+      </c>
+      <c r="C334" t="s">
+        <v>656</v>
+      </c>
+      <c r="E334" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335">
+        <v>2018</v>
+      </c>
+      <c r="B335" t="s">
+        <v>657</v>
+      </c>
+      <c r="C335" t="s">
+        <v>658</v>
+      </c>
+      <c r="E335" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336">
+        <v>2019</v>
+      </c>
+      <c r="B336" t="s">
+        <v>659</v>
+      </c>
+      <c r="C336" t="s">
+        <v>660</v>
+      </c>
+      <c r="E336" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337">
+        <v>2020</v>
+      </c>
+      <c r="B337" t="s">
+        <v>661</v>
+      </c>
+      <c r="C337" t="s">
+        <v>662</v>
+      </c>
+      <c r="E337" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338">
+        <v>2021</v>
+      </c>
+      <c r="B338" t="s">
+        <v>663</v>
+      </c>
+      <c r="C338" t="s">
+        <v>662</v>
+      </c>
+      <c r="E338" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339">
+        <v>2022</v>
+      </c>
+      <c r="B339" t="s">
+        <v>664</v>
+      </c>
+      <c r="C339" t="s">
+        <v>665</v>
+      </c>
+      <c r="E339" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340">
+        <v>2023</v>
+      </c>
+      <c r="B340" t="s">
+        <v>666</v>
+      </c>
+      <c r="C340" t="s">
+        <v>667</v>
+      </c>
+      <c r="E340" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341">
+        <v>2024</v>
+      </c>
+      <c r="B341" t="s">
+        <v>668</v>
+      </c>
+      <c r="C341" t="s">
+        <v>669</v>
+      </c>
+      <c r="E341" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342">
+        <v>2025</v>
+      </c>
+      <c r="B342" t="s">
+        <v>670</v>
+      </c>
+      <c r="C342" t="s">
+        <v>671</v>
+      </c>
+      <c r="E342" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343">
+        <v>2026</v>
+      </c>
+      <c r="B343" t="s">
+        <v>672</v>
+      </c>
+      <c r="C343" t="s">
+        <v>673</v>
+      </c>
+      <c r="E343" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344">
+        <v>2027</v>
+      </c>
+      <c r="B344" t="s">
+        <v>674</v>
+      </c>
+      <c r="C344" t="s">
+        <v>675</v>
+      </c>
+      <c r="E344" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345">
+        <v>2028</v>
+      </c>
+      <c r="B345" t="s">
+        <v>676</v>
+      </c>
+      <c r="C345" t="s">
+        <v>677</v>
+      </c>
+      <c r="E345" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346">
+        <v>2029</v>
+      </c>
+      <c r="B346" t="s">
+        <v>678</v>
+      </c>
+      <c r="C346" t="s">
+        <v>679</v>
+      </c>
+      <c r="E346" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347">
+        <v>2030</v>
+      </c>
+      <c r="B347" t="s">
+        <v>680</v>
+      </c>
+      <c r="C347" t="s">
+        <v>681</v>
+      </c>
+      <c r="E347" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348">
+        <v>2031</v>
+      </c>
+      <c r="B348" t="s">
+        <v>682</v>
+      </c>
+      <c r="C348" t="s">
+        <v>683</v>
+      </c>
+      <c r="E348" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349">
+        <v>2032</v>
+      </c>
+      <c r="B349" t="s">
+        <v>684</v>
+      </c>
+      <c r="C349" t="s">
+        <v>685</v>
+      </c>
+      <c r="E349" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350">
+        <v>2033</v>
+      </c>
+      <c r="B350" t="s">
+        <v>686</v>
+      </c>
+      <c r="C350" t="s">
+        <v>687</v>
+      </c>
+      <c r="E350" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351">
+        <v>2034</v>
+      </c>
+      <c r="B351" t="s">
+        <v>688</v>
+      </c>
+      <c r="C351" t="s">
+        <v>689</v>
+      </c>
+      <c r="E351" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352">
+        <v>2035</v>
+      </c>
+      <c r="B352" t="s">
+        <v>690</v>
+      </c>
+      <c r="C352" t="s">
+        <v>691</v>
+      </c>
+      <c r="E352" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353">
+        <v>2036</v>
+      </c>
+      <c r="B353" t="s">
+        <v>692</v>
+      </c>
+      <c r="C353" t="s">
+        <v>693</v>
+      </c>
+      <c r="E353" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354">
+        <v>2037</v>
+      </c>
+      <c r="B354" t="s">
+        <v>694</v>
+      </c>
+      <c r="C354" t="s">
+        <v>695</v>
+      </c>
+      <c r="E354" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355">
+        <v>2038</v>
+      </c>
+      <c r="B355" t="s">
+        <v>696</v>
+      </c>
+      <c r="C355" t="s">
+        <v>697</v>
+      </c>
+      <c r="E355" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356">
+        <v>2039</v>
+      </c>
+      <c r="B356" t="s">
+        <v>698</v>
+      </c>
+      <c r="C356" t="s">
+        <v>699</v>
+      </c>
+      <c r="E356" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357">
+        <v>2040</v>
+      </c>
+      <c r="B357" t="s">
+        <v>700</v>
+      </c>
+      <c r="C357" t="s">
+        <v>701</v>
+      </c>
+      <c r="E357" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358">
+        <v>2041</v>
+      </c>
+      <c r="B358" t="s">
+        <v>702</v>
+      </c>
+      <c r="C358" t="s">
+        <v>703</v>
+      </c>
+      <c r="E358" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359">
+        <v>2042</v>
+      </c>
+      <c r="B359" t="s">
+        <v>704</v>
+      </c>
+      <c r="C359" t="s">
+        <v>705</v>
+      </c>
+      <c r="E359" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360">
+        <v>2043</v>
+      </c>
+      <c r="B360" t="s">
+        <v>706</v>
+      </c>
+      <c r="C360" t="s">
+        <v>707</v>
+      </c>
+      <c r="E360" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361">
+        <v>2044</v>
+      </c>
+      <c r="B361" t="s">
+        <v>708</v>
+      </c>
+      <c r="C361" t="s">
+        <v>709</v>
+      </c>
+      <c r="E361" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362">
+        <v>2045</v>
+      </c>
+      <c r="B362" t="s">
+        <v>708</v>
+      </c>
+      <c r="C362" t="s">
+        <v>710</v>
+      </c>
+      <c r="E362" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363">
+        <v>2046</v>
+      </c>
+      <c r="B363" t="s">
+        <v>711</v>
+      </c>
+      <c r="C363" t="s">
+        <v>712</v>
+      </c>
+      <c r="E363" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364">
+        <v>2047</v>
+      </c>
+      <c r="B364" t="s">
+        <v>713</v>
+      </c>
+      <c r="C364" t="s">
+        <v>714</v>
+      </c>
+      <c r="E364" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365">
+        <v>2048</v>
+      </c>
+      <c r="B365" t="s">
+        <v>715</v>
+      </c>
+      <c r="C365" t="s">
+        <v>716</v>
+      </c>
+      <c r="E365" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366">
+        <v>2049</v>
+      </c>
+      <c r="B366" t="s">
+        <v>717</v>
+      </c>
+      <c r="C366" t="s">
+        <v>718</v>
+      </c>
+      <c r="E366" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367">
+        <v>2050</v>
+      </c>
+      <c r="B367" t="s">
+        <v>719</v>
+      </c>
+      <c r="C367" t="s">
+        <v>720</v>
+      </c>
+      <c r="E367" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368">
+        <v>2051</v>
+      </c>
+      <c r="B368" t="s">
+        <v>721</v>
+      </c>
+      <c r="C368" t="s">
+        <v>722</v>
+      </c>
+      <c r="E368" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369">
+        <v>2052</v>
+      </c>
+      <c r="B369" t="s">
+        <v>723</v>
+      </c>
+      <c r="C369" t="s">
+        <v>724</v>
+      </c>
+      <c r="E369" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370">
+        <v>2053</v>
+      </c>
+      <c r="B370" t="s">
+        <v>725</v>
+      </c>
+      <c r="C370" t="s">
+        <v>726</v>
+      </c>
+      <c r="E370" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371">
+        <v>2054</v>
+      </c>
+      <c r="B371" t="s">
+        <v>727</v>
+      </c>
+      <c r="C371" t="s">
+        <v>728</v>
+      </c>
+      <c r="E371" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372">
+        <v>2055</v>
+      </c>
+      <c r="B372" t="s">
+        <v>729</v>
+      </c>
+      <c r="C372" t="s">
+        <v>730</v>
+      </c>
+      <c r="E372" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373">
+        <v>2056</v>
+      </c>
+      <c r="B373" t="s">
+        <v>731</v>
+      </c>
+      <c r="C373" t="s">
+        <v>732</v>
+      </c>
+      <c r="E373" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374">
+        <v>2057</v>
+      </c>
+      <c r="B374" t="s">
+        <v>733</v>
+      </c>
+      <c r="C374" t="s">
+        <v>734</v>
+      </c>
+      <c r="E374" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375">
+        <v>2058</v>
+      </c>
+      <c r="B375" t="s">
+        <v>735</v>
+      </c>
+      <c r="C375" t="s">
+        <v>736</v>
+      </c>
+      <c r="E375" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376">
+        <v>2059</v>
+      </c>
+      <c r="B376" t="s">
+        <v>737</v>
+      </c>
+      <c r="C376" t="s">
+        <v>738</v>
+      </c>
+      <c r="E376" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377">
+        <v>2060</v>
+      </c>
+      <c r="B377" t="s">
+        <v>739</v>
+      </c>
+      <c r="C377" t="s">
+        <v>740</v>
+      </c>
+      <c r="E377" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378">
+        <v>2061</v>
+      </c>
+      <c r="B378" t="s">
+        <v>741</v>
+      </c>
+      <c r="C378" t="s">
+        <v>742</v>
+      </c>
+      <c r="E378" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379">
+        <v>2062</v>
+      </c>
+      <c r="B379" t="s">
+        <v>405</v>
+      </c>
+      <c r="C379" t="s">
+        <v>743</v>
+      </c>
+      <c r="E379" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380">
+        <v>2063</v>
+      </c>
+      <c r="B380" t="s">
+        <v>744</v>
+      </c>
+      <c r="C380" t="s">
+        <v>745</v>
+      </c>
+      <c r="E380" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381">
+        <v>2064</v>
+      </c>
+      <c r="B381" t="s">
+        <v>405</v>
+      </c>
+      <c r="C381" t="s">
+        <v>746</v>
+      </c>
+      <c r="E381" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382">
+        <v>2065</v>
+      </c>
+      <c r="B382" t="s">
+        <v>747</v>
+      </c>
+      <c r="C382" t="s">
+        <v>748</v>
+      </c>
+      <c r="E382" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383">
+        <v>2066</v>
+      </c>
+      <c r="B383" t="s">
+        <v>749</v>
+      </c>
+      <c r="C383" t="s">
+        <v>750</v>
+      </c>
+      <c r="E383" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384">
+        <v>2067</v>
+      </c>
+      <c r="B384" t="s">
+        <v>751</v>
+      </c>
+      <c r="C384" t="s">
+        <v>752</v>
+      </c>
+      <c r="E384" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385">
+        <v>2068</v>
+      </c>
+      <c r="B385" t="s">
+        <v>753</v>
+      </c>
+      <c r="C385" t="s">
+        <v>754</v>
+      </c>
+      <c r="E385" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386">
+        <v>2069</v>
+      </c>
+      <c r="B386" t="s">
+        <v>694</v>
+      </c>
+      <c r="C386" t="s">
+        <v>755</v>
+      </c>
+      <c r="E386" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387">
+        <v>2070</v>
+      </c>
+      <c r="B387" t="s">
+        <v>756</v>
+      </c>
+      <c r="C387" t="s">
+        <v>757</v>
+      </c>
+      <c r="E387" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388">
+        <v>2071</v>
+      </c>
+      <c r="B388" t="s">
+        <v>758</v>
+      </c>
+      <c r="C388" t="s">
+        <v>759</v>
+      </c>
+      <c r="E388" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389">
+        <v>2072</v>
+      </c>
+      <c r="B389" t="s">
+        <v>760</v>
+      </c>
+      <c r="C389" t="s">
+        <v>761</v>
+      </c>
+      <c r="E389" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390">
+        <v>2073</v>
+      </c>
+      <c r="B390" t="s">
+        <v>762</v>
+      </c>
+      <c r="C390" t="s">
+        <v>763</v>
+      </c>
+      <c r="E390" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391">
+        <v>2074</v>
+      </c>
+      <c r="B391" t="s">
+        <v>764</v>
+      </c>
+      <c r="C391" t="s">
+        <v>765</v>
+      </c>
+      <c r="E391" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392">
+        <v>2075</v>
+      </c>
+      <c r="B392" t="s">
+        <v>766</v>
+      </c>
+      <c r="C392" t="s">
+        <v>767</v>
+      </c>
+      <c r="E392" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393">
+        <v>2076</v>
+      </c>
+      <c r="B393" t="s">
+        <v>727</v>
+      </c>
+      <c r="C393" t="s">
+        <v>768</v>
+      </c>
+      <c r="E393" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394">
+        <v>2077</v>
+      </c>
+      <c r="B394" t="s">
+        <v>769</v>
+      </c>
+      <c r="C394" t="s">
+        <v>770</v>
+      </c>
+      <c r="E394" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395">
+        <v>2078</v>
+      </c>
+      <c r="B395" t="s">
+        <v>771</v>
+      </c>
+      <c r="C395" t="s">
+        <v>767</v>
+      </c>
+      <c r="E395" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396">
+        <v>2079</v>
+      </c>
+      <c r="B396" t="s">
+        <v>727</v>
+      </c>
+      <c r="C396" t="s">
+        <v>772</v>
+      </c>
+      <c r="E396" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397">
+        <v>2080</v>
+      </c>
+      <c r="B397" t="s">
+        <v>773</v>
+      </c>
+      <c r="C397" t="s">
+        <v>774</v>
+      </c>
+      <c r="E397" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398">
+        <v>2081</v>
+      </c>
+      <c r="B398" t="s">
+        <v>775</v>
+      </c>
+      <c r="C398" t="s">
+        <v>776</v>
+      </c>
+      <c r="E398" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399">
+        <v>2082</v>
+      </c>
+      <c r="B399" t="s">
+        <v>777</v>
+      </c>
+      <c r="C399" t="s">
+        <v>778</v>
+      </c>
+      <c r="E399" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400">
+        <v>2083</v>
+      </c>
+      <c r="B400" t="s">
+        <v>779</v>
+      </c>
+      <c r="C400" t="s">
+        <v>780</v>
+      </c>
+      <c r="E400" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401">
+        <v>2084</v>
+      </c>
+      <c r="B401" t="s">
+        <v>781</v>
+      </c>
+      <c r="C401" t="s">
+        <v>782</v>
+      </c>
+      <c r="E401" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402">
+        <v>2085</v>
+      </c>
+      <c r="B402" t="s">
+        <v>783</v>
+      </c>
+      <c r="C402" t="s">
+        <v>784</v>
+      </c>
+      <c r="E402" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403">
+        <v>2086</v>
+      </c>
+      <c r="B403" t="s">
+        <v>785</v>
+      </c>
+      <c r="C403" t="s">
+        <v>786</v>
+      </c>
+      <c r="E403" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404">
+        <v>2087</v>
+      </c>
+      <c r="B404" t="s">
+        <v>783</v>
+      </c>
+      <c r="C404" t="s">
+        <v>787</v>
+      </c>
+      <c r="E404" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405">
+        <v>2088</v>
+      </c>
+      <c r="B405" t="s">
+        <v>788</v>
+      </c>
+      <c r="C405" t="s">
+        <v>789</v>
+      </c>
+      <c r="E405" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406">
+        <v>2089</v>
+      </c>
+      <c r="B406" t="s">
+        <v>790</v>
+      </c>
+      <c r="C406" t="s">
+        <v>791</v>
+      </c>
+      <c r="E406" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407">
+        <v>2090</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="C407" t="s">
+        <v>793</v>
+      </c>
+      <c r="E407" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408">
+        <v>2091</v>
+      </c>
+      <c r="B408" t="s">
+        <v>794</v>
+      </c>
+      <c r="C408" t="s">
+        <v>795</v>
+      </c>
+      <c r="E408" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409">
+        <v>2092</v>
+      </c>
+      <c r="B409" t="s">
+        <v>796</v>
+      </c>
+      <c r="C409" t="s">
+        <v>797</v>
+      </c>
+      <c r="E409" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410">
+        <v>2093</v>
+      </c>
+      <c r="B410" t="s">
+        <v>798</v>
+      </c>
+      <c r="C410" t="s">
+        <v>799</v>
+      </c>
+      <c r="E410" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411">
+        <v>2094</v>
+      </c>
+      <c r="B411" t="s">
+        <v>800</v>
+      </c>
+      <c r="C411" t="s">
+        <v>801</v>
+      </c>
+      <c r="E411" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412">
+        <v>2095</v>
+      </c>
+      <c r="B412" t="s">
+        <v>802</v>
+      </c>
+      <c r="C412" t="s">
+        <v>803</v>
+      </c>
+      <c r="E412" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413">
+        <v>2096</v>
+      </c>
+      <c r="B413" t="s">
+        <v>804</v>
+      </c>
+      <c r="C413" t="s">
+        <v>805</v>
+      </c>
+      <c r="E413" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414">
+        <v>2097</v>
+      </c>
+      <c r="B414" t="s">
+        <v>806</v>
+      </c>
+      <c r="C414" t="s">
+        <v>807</v>
+      </c>
+      <c r="E414" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415">
+        <v>2098</v>
+      </c>
+      <c r="B415" t="s">
+        <v>808</v>
+      </c>
+      <c r="C415" t="s">
+        <v>809</v>
+      </c>
+      <c r="E415" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416">
+        <v>3001</v>
+      </c>
+      <c r="B416" t="s">
+        <v>810</v>
+      </c>
+      <c r="C416" t="s">
+        <v>811</v>
+      </c>
+      <c r="D416" t="s">
+        <v>812</v>
+      </c>
+      <c r="E416" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417">
+        <v>3002</v>
+      </c>
+      <c r="B417" t="s">
+        <v>814</v>
+      </c>
+      <c r="C417" t="s">
+        <v>815</v>
+      </c>
+      <c r="D417" t="s">
+        <v>816</v>
+      </c>
+      <c r="E417" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>
